--- a/data/backtest_3mo.xlsx
+++ b/data/backtest_3mo.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K165"/>
+  <dimension ref="A1:K167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,10 +501,10 @@
         <v>5188.777</v>
       </c>
       <c r="G2" t="n">
-        <v>5197.777</v>
+        <v>5195.527</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2</v>
+        <v>0.89</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -512,10 +512,10 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>-45</v>
+        <v>-200.25</v>
       </c>
       <c r="K2" t="n">
-        <v>9955</v>
+        <v>9799.75</v>
       </c>
     </row>
     <row r="3">
@@ -542,10 +542,10 @@
         <v>5173.315</v>
       </c>
       <c r="G3" t="n">
-        <v>5177.315</v>
+        <v>5176.315</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -553,10 +553,10 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="K3" t="n">
-        <v>10015</v>
+        <v>9999.75</v>
       </c>
     </row>
     <row r="4">
@@ -583,10 +583,10 @@
         <v>5176.636</v>
       </c>
       <c r="G4" t="n">
-        <v>5172.636</v>
+        <v>5173.636</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="K4" t="n">
-        <v>10075</v>
+        <v>10199.75</v>
       </c>
     </row>
     <row r="5">
@@ -624,10 +624,10 @@
         <v>5155.599</v>
       </c>
       <c r="G5" t="n">
-        <v>5150.515000000001</v>
+        <v>5151.786000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -635,10 +635,10 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>76.26000000000001</v>
+        <v>254.2</v>
       </c>
       <c r="K5" t="n">
-        <v>10151.26</v>
+        <v>10453.95</v>
       </c>
     </row>
     <row r="6">
@@ -665,10 +665,10 @@
         <v>5172.883</v>
       </c>
       <c r="G6" t="n">
-        <v>5176.883</v>
+        <v>5175.883</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>-20</v>
+        <v>-100</v>
       </c>
       <c r="K6" t="n">
-        <v>10131.26</v>
+        <v>10353.95</v>
       </c>
     </row>
     <row r="7">
@@ -706,10 +706,10 @@
         <v>5152.186</v>
       </c>
       <c r="G7" t="n">
-        <v>5156.186</v>
+        <v>5155.186</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="K7" t="n">
-        <v>10191.26</v>
+        <v>10553.95</v>
       </c>
     </row>
     <row r="8">
@@ -747,10 +747,10 @@
         <v>5106.619</v>
       </c>
       <c r="G8" t="n">
-        <v>5110.619</v>
+        <v>5109.619</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="K8" t="n">
-        <v>10251.26</v>
+        <v>10753.95</v>
       </c>
     </row>
     <row r="9">
@@ -788,10 +788,10 @@
         <v>5028.465</v>
       </c>
       <c r="G9" t="n">
-        <v>5024.465</v>
+        <v>5025.465</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -799,10 +799,10 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="K9" t="n">
-        <v>10311.26</v>
+        <v>10953.95</v>
       </c>
     </row>
     <row r="10">
@@ -829,10 +829,10 @@
         <v>5023.112</v>
       </c>
       <c r="G10" t="n">
-        <v>5014.443999999999</v>
+        <v>5016.610999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>-43.34</v>
+        <v>-216.7</v>
       </c>
       <c r="K10" t="n">
-        <v>10267.92</v>
+        <v>10737.25</v>
       </c>
     </row>
     <row r="11">
@@ -870,10 +870,10 @@
         <v>4996.8</v>
       </c>
       <c r="G11" t="n">
-        <v>5000.8</v>
+        <v>4999.8</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>-20</v>
+        <v>-100</v>
       </c>
       <c r="K11" t="n">
-        <v>10247.92</v>
+        <v>10637.25</v>
       </c>
     </row>
     <row r="12">
@@ -911,10 +911,10 @@
         <v>5006.536</v>
       </c>
       <c r="G12" t="n">
-        <v>4992.944</v>
+        <v>4996.342</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2</v>
+        <v>0.63</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>-67.95999999999999</v>
+        <v>-214.07</v>
       </c>
       <c r="K12" t="n">
-        <v>10179.96</v>
+        <v>10423.18</v>
       </c>
     </row>
     <row r="13">
@@ -952,10 +952,10 @@
         <v>4997.712</v>
       </c>
       <c r="G13" t="n">
-        <v>5001.712</v>
+        <v>5000.712</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="K13" t="n">
-        <v>10239.96</v>
+        <v>10623.18</v>
       </c>
     </row>
     <row r="14">
@@ -993,10 +993,10 @@
         <v>5010.579</v>
       </c>
       <c r="G14" t="n">
-        <v>5006.579</v>
+        <v>5007.579</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1004,10 +1004,10 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="K14" t="n">
-        <v>10299.96</v>
+        <v>10823.18</v>
       </c>
     </row>
     <row r="15">
@@ -1034,10 +1034,10 @@
         <v>4991.468</v>
       </c>
       <c r="G15" t="n">
-        <v>4995.468</v>
+        <v>4994.468</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="K15" t="n">
-        <v>10359.96</v>
+        <v>11023.18</v>
       </c>
     </row>
     <row r="16">
@@ -1075,10 +1075,10 @@
         <v>4841.279</v>
       </c>
       <c r="G16" t="n">
-        <v>4845.279</v>
+        <v>4844.279</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1086,10 +1086,10 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="K16" t="n">
-        <v>10419.96</v>
+        <v>11223.18</v>
       </c>
     </row>
     <row r="17">
@@ -1116,10 +1116,10 @@
         <v>4640.222</v>
       </c>
       <c r="G17" t="n">
-        <v>4632.665999999999</v>
+        <v>4634.554999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1127,10 +1127,10 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>-37.78</v>
+        <v>-188.9</v>
       </c>
       <c r="K17" t="n">
-        <v>10382.18</v>
+        <v>11034.28</v>
       </c>
     </row>
     <row r="18">
@@ -1157,10 +1157,10 @@
         <v>4715.404</v>
       </c>
       <c r="G18" t="n">
-        <v>4726.9</v>
+        <v>4724.026</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2</v>
+        <v>0.77</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>-57.48</v>
+        <v>-221.3</v>
       </c>
       <c r="K18" t="n">
-        <v>10324.7</v>
+        <v>10812.98</v>
       </c>
     </row>
     <row r="19">
@@ -1198,10 +1198,10 @@
         <v>4659.81</v>
       </c>
       <c r="G19" t="n">
-        <v>4670.434</v>
+        <v>4667.778</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>-53.12</v>
+        <v>-215.14</v>
       </c>
       <c r="K19" t="n">
-        <v>10271.58</v>
+        <v>10597.84</v>
       </c>
     </row>
     <row r="20">
@@ -1239,10 +1239,10 @@
         <v>4349.417</v>
       </c>
       <c r="G20" t="n">
-        <v>4358.737</v>
+        <v>4356.407</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2</v>
+        <v>0.91</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>139.8</v>
+        <v>424.06</v>
       </c>
       <c r="K20" t="n">
-        <v>10411.38</v>
+        <v>11021.9</v>
       </c>
     </row>
     <row r="21">
@@ -1280,10 +1280,10 @@
         <v>4400.499</v>
       </c>
       <c r="G21" t="n">
-        <v>4406.422999999999</v>
+        <v>4404.941999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1291,10 +1291,10 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>88.86</v>
+        <v>296.2</v>
       </c>
       <c r="K21" t="n">
-        <v>10500.24</v>
+        <v>11318.1</v>
       </c>
     </row>
     <row r="22">
@@ -1321,21 +1321,21 @@
         <v>4564.007</v>
       </c>
       <c r="G22" t="n">
-        <v>4568.007</v>
+        <v>4567.007</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>-20</v>
+        <v>200</v>
       </c>
       <c r="K22" t="n">
-        <v>10480.24</v>
+        <v>11518.1</v>
       </c>
     </row>
     <row r="23">
@@ -1362,10 +1362,10 @@
         <v>4568.243</v>
       </c>
       <c r="G23" t="n">
-        <v>4564.243</v>
+        <v>4565.243</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1373,10 +1373,10 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="K23" t="n">
-        <v>10540.24</v>
+        <v>11718.1</v>
       </c>
     </row>
     <row r="24">
@@ -1403,10 +1403,10 @@
         <v>4559.475</v>
       </c>
       <c r="G24" t="n">
-        <v>4564.282999999998</v>
+        <v>4563.080999999998</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>72.12</v>
+        <v>240.4</v>
       </c>
       <c r="K24" t="n">
-        <v>10612.36</v>
+        <v>11958.5</v>
       </c>
     </row>
     <row r="25">
@@ -1444,10 +1444,10 @@
         <v>4531.286</v>
       </c>
       <c r="G25" t="n">
-        <v>4535.286</v>
+        <v>4534.286</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1455,10 +1455,10 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>-20</v>
+        <v>-100</v>
       </c>
       <c r="K25" t="n">
-        <v>10592.36</v>
+        <v>11858.5</v>
       </c>
     </row>
     <row r="26">
@@ -1485,10 +1485,10 @@
         <v>4526.603</v>
       </c>
       <c r="G26" t="n">
-        <v>4521.047</v>
+        <v>4522.436</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>-27.78</v>
+        <v>-138.9</v>
       </c>
       <c r="K26" t="n">
-        <v>10564.58</v>
+        <v>11719.6</v>
       </c>
     </row>
     <row r="27">
@@ -1526,10 +1526,10 @@
         <v>4437.351</v>
       </c>
       <c r="G27" t="n">
-        <v>4448.195000000001</v>
+        <v>4445.484</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2</v>
+        <v>0.86</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1537,10 +1537,10 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>-54.22</v>
+        <v>-233.15</v>
       </c>
       <c r="K27" t="n">
-        <v>10510.36</v>
+        <v>11486.46</v>
       </c>
     </row>
     <row r="28">
@@ -1567,10 +1567,10 @@
         <v>4405.066</v>
       </c>
       <c r="G28" t="n">
-        <v>4401.066</v>
+        <v>4402.066</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1578,10 +1578,10 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="K28" t="n">
-        <v>10570.36</v>
+        <v>11686.46</v>
       </c>
     </row>
     <row r="29">
@@ -1608,10 +1608,10 @@
         <v>4416.84</v>
       </c>
       <c r="G29" t="n">
-        <v>4412.84</v>
+        <v>4413.84</v>
       </c>
       <c r="H29" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="K29" t="n">
-        <v>10630.36</v>
+        <v>11886.46</v>
       </c>
     </row>
     <row r="30">
@@ -1649,10 +1649,10 @@
         <v>4409.686</v>
       </c>
       <c r="G30" t="n">
-        <v>4422.818000000001</v>
+        <v>4419.535000000001</v>
       </c>
       <c r="H30" t="n">
-        <v>0.2</v>
+        <v>0.72</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1660,10 +1660,10 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>-65.66</v>
+        <v>-236.38</v>
       </c>
       <c r="K30" t="n">
-        <v>10564.7</v>
+        <v>11650.08</v>
       </c>
     </row>
     <row r="31">
@@ -1690,10 +1690,10 @@
         <v>4503.36</v>
       </c>
       <c r="G31" t="n">
-        <v>4507.36</v>
+        <v>4506.36</v>
       </c>
       <c r="H31" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1701,10 +1701,10 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="K31" t="n">
-        <v>10624.7</v>
+        <v>11850.08</v>
       </c>
     </row>
     <row r="32">
@@ -1731,10 +1731,10 @@
         <v>4507.025</v>
       </c>
       <c r="G32" t="n">
-        <v>4500.797</v>
+        <v>4502.354</v>
       </c>
       <c r="H32" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1742,10 +1742,10 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>-31.14</v>
+        <v>-155.7</v>
       </c>
       <c r="K32" t="n">
-        <v>10593.56</v>
+        <v>11694.38</v>
       </c>
     </row>
     <row r="33">
@@ -1772,21 +1772,21 @@
         <v>4522.227</v>
       </c>
       <c r="G33" t="n">
-        <v>4529.787000000001</v>
+        <v>4527.897000000001</v>
       </c>
       <c r="H33" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>-37.8</v>
+        <v>378</v>
       </c>
       <c r="K33" t="n">
-        <v>10555.76</v>
+        <v>12072.38</v>
       </c>
     </row>
     <row r="34">
@@ -1813,10 +1813,10 @@
         <v>4510.221</v>
       </c>
       <c r="G34" t="n">
-        <v>4514.221</v>
+        <v>4513.221</v>
       </c>
       <c r="H34" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -1824,10 +1824,10 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="K34" t="n">
-        <v>10615.76</v>
+        <v>12272.38</v>
       </c>
     </row>
     <row r="35">
@@ -1854,10 +1854,10 @@
         <v>4510.795</v>
       </c>
       <c r="G35" t="n">
-        <v>4515.855000000001</v>
+        <v>4514.590000000001</v>
       </c>
       <c r="H35" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -1865,10 +1865,10 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>75.90000000000001</v>
+        <v>253</v>
       </c>
       <c r="K35" t="n">
-        <v>10691.66</v>
+        <v>12525.38</v>
       </c>
     </row>
     <row r="36">
@@ -1895,10 +1895,10 @@
         <v>4558.616</v>
       </c>
       <c r="G36" t="n">
-        <v>4554.616</v>
+        <v>4555.616</v>
       </c>
       <c r="H36" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>-20</v>
+        <v>-100</v>
       </c>
       <c r="K36" t="n">
-        <v>10671.66</v>
+        <v>12425.38</v>
       </c>
     </row>
     <row r="37">
@@ -1936,10 +1936,10 @@
         <v>4576.746</v>
       </c>
       <c r="G37" t="n">
-        <v>4572.746</v>
+        <v>4573.746</v>
       </c>
       <c r="H37" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="K37" t="n">
-        <v>10731.66</v>
+        <v>12625.38</v>
       </c>
     </row>
     <row r="38">
@@ -1977,10 +1977,10 @@
         <v>4764.415</v>
       </c>
       <c r="G38" t="n">
-        <v>4755.567000000002</v>
+        <v>4757.779000000001</v>
       </c>
       <c r="H38" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -1988,10 +1988,10 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>132.72</v>
+        <v>442.4</v>
       </c>
       <c r="K38" t="n">
-        <v>10864.38</v>
+        <v>13067.78</v>
       </c>
     </row>
     <row r="39">
@@ -2018,10 +2018,10 @@
         <v>4671.984</v>
       </c>
       <c r="G39" t="n">
-        <v>4660.079999999998</v>
+        <v>4663.055999999999</v>
       </c>
       <c r="H39" t="n">
-        <v>0.2</v>
+        <v>0.88</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2029,10 +2029,10 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>-59.52</v>
+        <v>-261.89</v>
       </c>
       <c r="K39" t="n">
-        <v>10804.86</v>
+        <v>12805.89</v>
       </c>
     </row>
     <row r="40">
@@ -2059,10 +2059,10 @@
         <v>4661.31</v>
       </c>
       <c r="G40" t="n">
-        <v>4657.31</v>
+        <v>4658.31</v>
       </c>
       <c r="H40" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="K40" t="n">
-        <v>10864.86</v>
+        <v>13005.89</v>
       </c>
     </row>
     <row r="41">
@@ -2100,10 +2100,10 @@
         <v>4647.481</v>
       </c>
       <c r="G41" t="n">
-        <v>4658.553</v>
+        <v>4655.785</v>
       </c>
       <c r="H41" t="n">
-        <v>0.2</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2111,10 +2111,10 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>166.08</v>
+        <v>520.38</v>
       </c>
       <c r="K41" t="n">
-        <v>11030.94</v>
+        <v>13526.28</v>
       </c>
     </row>
     <row r="42">
@@ -2141,10 +2141,10 @@
         <v>4648.213</v>
       </c>
       <c r="G42" t="n">
-        <v>4644.097000000002</v>
+        <v>4645.126000000001</v>
       </c>
       <c r="H42" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>61.74</v>
+        <v>205.8</v>
       </c>
       <c r="K42" t="n">
-        <v>11092.68</v>
+        <v>13732.08</v>
       </c>
     </row>
     <row r="43">
@@ -2182,10 +2182,10 @@
         <v>4721.926</v>
       </c>
       <c r="G43" t="n">
-        <v>4717.926</v>
+        <v>4718.926</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="K43" t="n">
-        <v>11152.68</v>
+        <v>13932.08</v>
       </c>
     </row>
     <row r="44">
@@ -2223,10 +2223,10 @@
         <v>4761.343</v>
       </c>
       <c r="G44" t="n">
-        <v>4753.539</v>
+        <v>4755.49</v>
       </c>
       <c r="H44" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2234,10 +2234,10 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>-39.02</v>
+        <v>-195.1</v>
       </c>
       <c r="K44" t="n">
-        <v>11113.66</v>
+        <v>13736.98</v>
       </c>
     </row>
     <row r="45">
@@ -2245,7 +2245,7 @@
         <v>46122.17708333334</v>
       </c>
       <c r="B45" s="1" t="n">
-        <v>46122.23958333334</v>
+        <v>46122.19791666666</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -2264,51 +2264,51 @@
         <v>4769.051</v>
       </c>
       <c r="G45" t="n">
-        <v>4755.558999999998</v>
+        <v>4758.931999999999</v>
       </c>
       <c r="H45" t="n">
-        <v>0.2</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>-67.45999999999999</v>
+        <v>546.4299999999999</v>
       </c>
       <c r="K45" t="n">
-        <v>11046.2</v>
+        <v>14283.4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46122.36458333334</v>
+        <v>46122.23958333334</v>
       </c>
       <c r="B46" s="1" t="n">
-        <v>46122.375</v>
+        <v>46122.25</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>BOUNCE</t>
+          <t>BREAKOUT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4740.771</v>
+        <v>4766.096</v>
       </c>
       <c r="F46" t="n">
-        <v>4739.71</v>
+        <v>4769.051</v>
       </c>
       <c r="G46" t="n">
-        <v>4743.953999999999</v>
+        <v>4760.185999999998</v>
       </c>
       <c r="H46" t="n">
-        <v>0.2</v>
+        <v>0.97</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2316,63 +2316,63 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>63.66</v>
+        <v>573.27</v>
       </c>
       <c r="K46" t="n">
-        <v>11109.86</v>
+        <v>14856.67</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46122.38541666666</v>
+        <v>46122.36458333334</v>
       </c>
       <c r="B47" s="1" t="n">
-        <v>46122.40625</v>
+        <v>46122.375</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>BREAKOUT</t>
+          <t>BOUNCE</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4748.643</v>
+        <v>4740.771</v>
       </c>
       <c r="F47" t="n">
-        <v>4752.239</v>
+        <v>4739.71</v>
       </c>
       <c r="G47" t="n">
-        <v>4737.855000000001</v>
+        <v>4742.892999999999</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>-71.92</v>
+        <v>212.2</v>
       </c>
       <c r="K47" t="n">
-        <v>11037.94</v>
+        <v>15068.87</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46122.66666666666</v>
+        <v>46122.38541666666</v>
       </c>
       <c r="B48" s="1" t="n">
-        <v>46122.67708333334</v>
+        <v>46122.40625</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2381,16 +2381,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4763.002</v>
+        <v>4748.643</v>
       </c>
       <c r="F48" t="n">
-        <v>4759.151</v>
+        <v>4752.239</v>
       </c>
       <c r="G48" t="n">
-        <v>4774.555000000002</v>
+        <v>4741.451000000001</v>
       </c>
       <c r="H48" t="n">
-        <v>0.2</v>
+        <v>0.84</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2398,18 +2398,18 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>-77.02</v>
+        <v>-302.06</v>
       </c>
       <c r="K48" t="n">
-        <v>10960.92</v>
+        <v>14766.81</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46122.70833333334</v>
+        <v>46122.66666666666</v>
       </c>
       <c r="B49" s="1" t="n">
-        <v>46122.71875</v>
+        <v>46122.67708333334</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -2418,43 +2418,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>BOUNCE</t>
+          <t>BREAKOUT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4764.468</v>
+        <v>4763.002</v>
       </c>
       <c r="F49" t="n">
-        <v>4763.409</v>
+        <v>4759.151</v>
       </c>
       <c r="G49" t="n">
-        <v>4767.645</v>
+        <v>4770.704000000002</v>
       </c>
       <c r="H49" t="n">
-        <v>0.2</v>
+        <v>0.77</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>63.54</v>
+        <v>-296.53</v>
       </c>
       <c r="K49" t="n">
-        <v>11024.46</v>
+        <v>14470.28</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46122.73958333334</v>
+        <v>46122.70833333334</v>
       </c>
       <c r="B50" s="1" t="n">
-        <v>46122.75</v>
+        <v>46122.71875</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2463,16 +2463,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4760.388</v>
+        <v>4764.468</v>
       </c>
       <c r="F50" t="n">
-        <v>4762.151</v>
+        <v>4763.409</v>
       </c>
       <c r="G50" t="n">
-        <v>4755.099</v>
+        <v>4766.586</v>
       </c>
       <c r="H50" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2480,18 +2480,18 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>105.78</v>
+        <v>211.8</v>
       </c>
       <c r="K50" t="n">
-        <v>11130.24</v>
+        <v>14682.08</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46122.77083333334</v>
+        <v>46122.73958333334</v>
       </c>
       <c r="B51" s="1" t="n">
-        <v>46122.80208333334</v>
+        <v>46122.75</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -2504,35 +2504,35 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4768.213</v>
+        <v>4760.388</v>
       </c>
       <c r="F51" t="n">
-        <v>4770.162</v>
+        <v>4762.151</v>
       </c>
       <c r="G51" t="n">
-        <v>4762.365999999998</v>
+        <v>4756.862</v>
       </c>
       <c r="H51" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>-38.98</v>
+        <v>352.6</v>
       </c>
       <c r="K51" t="n">
-        <v>11091.26</v>
+        <v>15034.68</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46122.82291666666</v>
+        <v>46122.77083333334</v>
       </c>
       <c r="B52" s="1" t="n">
-        <v>46122.83333333334</v>
+        <v>46122.78125</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2545,16 +2545,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4759.73</v>
+        <v>4768.213</v>
       </c>
       <c r="F52" t="n">
-        <v>4762.151</v>
+        <v>4770.162</v>
       </c>
       <c r="G52" t="n">
-        <v>4752.466999999999</v>
+        <v>4764.314999999999</v>
       </c>
       <c r="H52" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -2562,40 +2562,40 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>145.26</v>
+        <v>389.8</v>
       </c>
       <c r="K52" t="n">
-        <v>11236.52</v>
+        <v>15424.48</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46125.28125</v>
+        <v>46122.82291666666</v>
       </c>
       <c r="B53" s="1" t="n">
-        <v>46125.29166666666</v>
+        <v>46122.83333333334</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>BREAKOUT</t>
+          <t>BOUNCE</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4725.415</v>
+        <v>4759.73</v>
       </c>
       <c r="F53" t="n">
-        <v>4722.323</v>
+        <v>4762.151</v>
       </c>
       <c r="G53" t="n">
-        <v>4734.690999999999</v>
+        <v>4754.887999999999</v>
       </c>
       <c r="H53" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -2603,40 +2603,40 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>185.52</v>
+        <v>484.2</v>
       </c>
       <c r="K53" t="n">
-        <v>11422.04</v>
+        <v>15908.68</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46125.36458333334</v>
+        <v>46125.28125</v>
       </c>
       <c r="B54" s="1" t="n">
-        <v>46125.375</v>
+        <v>46125.29166666666</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>BOUNCE</t>
+          <t>BREAKOUT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4723.423</v>
+        <v>4725.415</v>
       </c>
       <c r="F54" t="n">
-        <v>4725.323</v>
+        <v>4722.323</v>
       </c>
       <c r="G54" t="n">
-        <v>4717.722999999998</v>
+        <v>4731.598999999999</v>
       </c>
       <c r="H54" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -2644,18 +2644,18 @@
         </is>
       </c>
       <c r="J54" t="n">
-        <v>114</v>
+        <v>618.4</v>
       </c>
       <c r="K54" t="n">
-        <v>11536.04</v>
+        <v>16527.08</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46125.45833333334</v>
+        <v>46125.36458333334</v>
       </c>
       <c r="B55" s="1" t="n">
-        <v>46125.46875</v>
+        <v>46125.375</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2664,20 +2664,20 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>BREAKOUT</t>
+          <t>BOUNCE</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4721.587</v>
+        <v>4723.423</v>
       </c>
       <c r="F55" t="n">
-        <v>4722.587</v>
+        <v>4725.323</v>
       </c>
       <c r="G55" t="n">
-        <v>4718.587</v>
+        <v>4719.622999999999</v>
       </c>
       <c r="H55" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -2685,18 +2685,18 @@
         </is>
       </c>
       <c r="J55" t="n">
-        <v>60</v>
+        <v>380</v>
       </c>
       <c r="K55" t="n">
-        <v>11596.04</v>
+        <v>16907.08</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46125.72916666666</v>
+        <v>46125.45833333334</v>
       </c>
       <c r="B56" s="1" t="n">
-        <v>46125.73958333334</v>
+        <v>46125.46875</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2705,20 +2705,20 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>BOUNCE</t>
+          <t>BREAKOUT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4743.856</v>
+        <v>4721.587</v>
       </c>
       <c r="F56" t="n">
-        <v>4746.069</v>
+        <v>4722.587</v>
       </c>
       <c r="G56" t="n">
-        <v>4737.216999999998</v>
+        <v>4719.587</v>
       </c>
       <c r="H56" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -2726,18 +2726,18 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>132.78</v>
+        <v>200</v>
       </c>
       <c r="K56" t="n">
-        <v>11728.82</v>
+        <v>17107.08</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46126.07291666666</v>
+        <v>46125.72916666666</v>
       </c>
       <c r="B57" s="1" t="n">
-        <v>46126.08333333334</v>
+        <v>46125.73958333334</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -2750,35 +2750,35 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4764.584</v>
+        <v>4743.856</v>
       </c>
       <c r="F57" t="n">
-        <v>4767.491</v>
+        <v>4746.069</v>
       </c>
       <c r="G57" t="n">
-        <v>4755.862999999999</v>
+        <v>4739.429999999998</v>
       </c>
       <c r="H57" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>-58.14</v>
+        <v>442.6</v>
       </c>
       <c r="K57" t="n">
-        <v>11670.68</v>
+        <v>17549.68</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46126.20833333334</v>
+        <v>46126.07291666666</v>
       </c>
       <c r="B58" s="1" t="n">
-        <v>46126.21875</v>
+        <v>46126.08333333334</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -2791,16 +2791,16 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4765.37</v>
+        <v>4764.584</v>
       </c>
       <c r="F58" t="n">
         <v>4767.491</v>
       </c>
       <c r="G58" t="n">
-        <v>4759.007</v>
+        <v>4758.77</v>
       </c>
       <c r="H58" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -2808,40 +2808,40 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>-42.42</v>
+        <v>-290.7</v>
       </c>
       <c r="K58" t="n">
-        <v>11628.26</v>
+        <v>17258.98</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46126.39583333334</v>
+        <v>46126.20833333334</v>
       </c>
       <c r="B59" s="1" t="n">
-        <v>46126.40625</v>
+        <v>46126.21875</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>BREAKOUT</t>
+          <t>BOUNCE</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4778.219</v>
+        <v>4765.37</v>
       </c>
       <c r="F59" t="n">
-        <v>4775.47</v>
+        <v>4767.491</v>
       </c>
       <c r="G59" t="n">
-        <v>4786.465999999999</v>
+        <v>4761.128</v>
       </c>
       <c r="H59" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -2849,40 +2849,40 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>-54.98</v>
+        <v>-212.1</v>
       </c>
       <c r="K59" t="n">
-        <v>11573.28</v>
+        <v>17046.88</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46126.55208333334</v>
+        <v>46126.39583333334</v>
       </c>
       <c r="B60" s="1" t="n">
-        <v>46126.5625</v>
+        <v>46126.40625</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>BOUNCE</t>
+          <t>BREAKOUT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4782.977</v>
+        <v>4778.219</v>
       </c>
       <c r="F60" t="n">
-        <v>4784.488</v>
+        <v>4775.47</v>
       </c>
       <c r="G60" t="n">
-        <v>4778.443999999999</v>
+        <v>4783.717</v>
       </c>
       <c r="H60" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -2890,18 +2890,18 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>-30.22</v>
+        <v>-274.9</v>
       </c>
       <c r="K60" t="n">
-        <v>11543.06</v>
+        <v>16771.98</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46126.58333333334</v>
+        <v>46126.55208333334</v>
       </c>
       <c r="B61" s="1" t="n">
-        <v>46126.59375</v>
+        <v>46126.5625</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -2914,16 +2914,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4794.921</v>
+        <v>4782.977</v>
       </c>
       <c r="F61" t="n">
-        <v>4797.892</v>
+        <v>4784.488</v>
       </c>
       <c r="G61" t="n">
-        <v>4786.008000000002</v>
+        <v>4779.954999999999</v>
       </c>
       <c r="H61" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -2931,22 +2931,22 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>-59.42</v>
+        <v>-151.1</v>
       </c>
       <c r="K61" t="n">
-        <v>11483.64</v>
+        <v>16620.88</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46127.30208333334</v>
+        <v>46126.58333333334</v>
       </c>
       <c r="B62" s="1" t="n">
-        <v>46127.3125</v>
+        <v>46126.59375</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2955,16 +2955,16 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4812.593</v>
+        <v>4794.921</v>
       </c>
       <c r="F62" t="n">
-        <v>4811.009</v>
+        <v>4797.892</v>
       </c>
       <c r="G62" t="n">
-        <v>4817.344999999999</v>
+        <v>4788.979000000001</v>
       </c>
       <c r="H62" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -2972,18 +2972,18 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>-31.68</v>
+        <v>-297.1</v>
       </c>
       <c r="K62" t="n">
-        <v>11451.96</v>
+        <v>16323.78</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46127.33333333334</v>
+        <v>46127.30208333334</v>
       </c>
       <c r="B63" s="1" t="n">
-        <v>46127.34375</v>
+        <v>46127.3125</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -2996,16 +2996,16 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4811.256</v>
+        <v>4812.593</v>
       </c>
       <c r="F63" t="n">
-        <v>4810.256</v>
+        <v>4811.009</v>
       </c>
       <c r="G63" t="n">
-        <v>4814.256</v>
+        <v>4815.761</v>
       </c>
       <c r="H63" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3013,18 +3013,18 @@
         </is>
       </c>
       <c r="J63" t="n">
-        <v>-20</v>
+        <v>-158.4</v>
       </c>
       <c r="K63" t="n">
-        <v>11431.96</v>
+        <v>16165.38</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46127.5</v>
+        <v>46127.33333333334</v>
       </c>
       <c r="B64" s="1" t="n">
-        <v>46127.51041666666</v>
+        <v>46127.34375</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -3037,35 +3037,35 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4813.781</v>
+        <v>4811.256</v>
       </c>
       <c r="F64" t="n">
-        <v>4811.009</v>
+        <v>4810.256</v>
       </c>
       <c r="G64" t="n">
-        <v>4822.097</v>
+        <v>4813.256</v>
       </c>
       <c r="H64" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>-55.44</v>
+        <v>200</v>
       </c>
       <c r="K64" t="n">
-        <v>11376.52</v>
+        <v>16365.38</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46127.66666666666</v>
+        <v>46127.5</v>
       </c>
       <c r="B65" s="1" t="n">
-        <v>46127.67708333334</v>
+        <v>46127.51041666666</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -3078,16 +3078,16 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4808.527</v>
+        <v>4813.781</v>
       </c>
       <c r="F65" t="n">
-        <v>4806.716</v>
+        <v>4811.009</v>
       </c>
       <c r="G65" t="n">
-        <v>4813.959999999999</v>
+        <v>4819.325</v>
       </c>
       <c r="H65" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3095,22 +3095,22 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>-36.22</v>
+        <v>-277.2</v>
       </c>
       <c r="K65" t="n">
-        <v>11340.3</v>
+        <v>16088.18</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46128.17708333334</v>
+        <v>46127.66666666666</v>
       </c>
       <c r="B66" s="1" t="n">
-        <v>46128.1875</v>
+        <v>46127.67708333334</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3119,39 +3119,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4826.243</v>
+        <v>4808.527</v>
       </c>
       <c r="F66" t="n">
-        <v>4828.428</v>
+        <v>4806.716</v>
       </c>
       <c r="G66" t="n">
-        <v>4819.688000000002</v>
+        <v>4812.148999999999</v>
       </c>
       <c r="H66" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>-43.7</v>
+        <v>362.2</v>
       </c>
       <c r="K66" t="n">
-        <v>11296.6</v>
+        <v>16450.38</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46128.35416666666</v>
+        <v>46128.17708333334</v>
       </c>
       <c r="B67" s="1" t="n">
-        <v>46128.36458333334</v>
+        <v>46128.1875</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3160,16 +3160,16 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4811.989</v>
+        <v>4826.243</v>
       </c>
       <c r="F67" t="n">
-        <v>4809.695</v>
+        <v>4828.428</v>
       </c>
       <c r="G67" t="n">
-        <v>4818.870999999999</v>
+        <v>4821.873000000001</v>
       </c>
       <c r="H67" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -3177,18 +3177,18 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>-45.88</v>
+        <v>-218.5</v>
       </c>
       <c r="K67" t="n">
-        <v>11250.72</v>
+        <v>16231.88</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46129</v>
+        <v>46128.35416666666</v>
       </c>
       <c r="B68" s="1" t="n">
-        <v>46129.01041666666</v>
+        <v>46128.36458333334</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -3201,39 +3201,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4789.968</v>
+        <v>4811.989</v>
       </c>
       <c r="F68" t="n">
-        <v>4788.968</v>
+        <v>4809.695</v>
       </c>
       <c r="G68" t="n">
-        <v>4792.968</v>
+        <v>4816.576999999999</v>
       </c>
       <c r="H68" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="J68" t="n">
-        <v>60</v>
+        <v>-229.4</v>
       </c>
       <c r="K68" t="n">
-        <v>11310.72</v>
+        <v>16002.48</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46129.39583333334</v>
+        <v>46129</v>
       </c>
       <c r="B69" s="1" t="n">
-        <v>46129.41666666666</v>
+        <v>46129.01041666666</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3242,16 +3242,16 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4794.62</v>
+        <v>4789.968</v>
       </c>
       <c r="F69" t="n">
-        <v>4796.228</v>
+        <v>4788.968</v>
       </c>
       <c r="G69" t="n">
-        <v>4789.795999999999</v>
+        <v>4791.968</v>
       </c>
       <c r="H69" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -3259,18 +3259,18 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>96.48</v>
+        <v>200</v>
       </c>
       <c r="K69" t="n">
-        <v>11407.2</v>
+        <v>16202.48</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46129.48958333334</v>
+        <v>46129.39583333334</v>
       </c>
       <c r="B70" s="1" t="n">
-        <v>46129.5</v>
+        <v>46129.40625</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -3283,39 +3283,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4799.193</v>
+        <v>4794.62</v>
       </c>
       <c r="F70" t="n">
-        <v>4800.193</v>
+        <v>4796.228</v>
       </c>
       <c r="G70" t="n">
-        <v>4796.193</v>
+        <v>4791.404</v>
       </c>
       <c r="H70" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>-20</v>
+        <v>321.6</v>
       </c>
       <c r="K70" t="n">
-        <v>11387.2</v>
+        <v>16524.08</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46133.04166666666</v>
+        <v>46129.41666666666</v>
       </c>
       <c r="B71" s="1" t="n">
-        <v>46133.05208333334</v>
+        <v>46129.42708333334</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3324,16 +3324,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4814.905</v>
+        <v>4791.212</v>
       </c>
       <c r="F71" t="n">
-        <v>4817.373</v>
+        <v>4789.456</v>
       </c>
       <c r="G71" t="n">
-        <v>4807.501</v>
+        <v>4794.724000000001</v>
       </c>
       <c r="H71" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -3341,22 +3341,22 @@
         </is>
       </c>
       <c r="J71" t="n">
-        <v>-49.36</v>
+        <v>-175.6</v>
       </c>
       <c r="K71" t="n">
-        <v>11337.84</v>
+        <v>16348.48</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46133.09375</v>
+        <v>46129.48958333334</v>
       </c>
       <c r="B72" s="1" t="n">
-        <v>46133.10416666666</v>
+        <v>46129.5</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3365,16 +3365,16 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4807.703</v>
+        <v>4799.193</v>
       </c>
       <c r="F72" t="n">
-        <v>4805.334</v>
+        <v>4800.193</v>
       </c>
       <c r="G72" t="n">
-        <v>4814.810000000002</v>
+        <v>4797.193</v>
       </c>
       <c r="H72" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -3382,18 +3382,18 @@
         </is>
       </c>
       <c r="J72" t="n">
-        <v>-47.38</v>
+        <v>-100</v>
       </c>
       <c r="K72" t="n">
-        <v>11290.46</v>
+        <v>16248.48</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46133.32291666666</v>
+        <v>46133.04166666666</v>
       </c>
       <c r="B73" s="1" t="n">
-        <v>46133.33333333334</v>
+        <v>46133.05208333334</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -3402,39 +3402,39 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>BREAKOUT</t>
+          <t>BOUNCE</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4786.082</v>
+        <v>4814.905</v>
       </c>
       <c r="F73" t="n">
-        <v>4787.259</v>
+        <v>4817.373</v>
       </c>
       <c r="G73" t="n">
-        <v>4782.551000000001</v>
+        <v>4809.969</v>
       </c>
       <c r="H73" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>70.62</v>
+        <v>-246.8</v>
       </c>
       <c r="K73" t="n">
-        <v>11361.08</v>
+        <v>16001.68</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46133.34375</v>
+        <v>46133.09375</v>
       </c>
       <c r="B74" s="1" t="n">
-        <v>46133.375</v>
+        <v>46133.10416666666</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -3447,16 +3447,16 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4787.023</v>
+        <v>4807.703</v>
       </c>
       <c r="F74" t="n">
-        <v>4784.259</v>
+        <v>4805.334</v>
       </c>
       <c r="G74" t="n">
-        <v>4795.315000000001</v>
+        <v>4812.441000000002</v>
       </c>
       <c r="H74" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -3464,104 +3464,104 @@
         </is>
       </c>
       <c r="J74" t="n">
-        <v>-55.28</v>
+        <v>-236.9</v>
       </c>
       <c r="K74" t="n">
-        <v>11305.8</v>
+        <v>15764.78</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46133.39583333334</v>
+        <v>46133.32291666666</v>
       </c>
       <c r="B75" s="1" t="n">
-        <v>46133.40625</v>
+        <v>46133.33333333334</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>BOUNCE</t>
+          <t>BREAKOUT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4787.055</v>
+        <v>4786.082</v>
       </c>
       <c r="F75" t="n">
-        <v>4784.259</v>
+        <v>4787.259</v>
       </c>
       <c r="G75" t="n">
-        <v>4795.443000000001</v>
+        <v>4783.728000000001</v>
       </c>
       <c r="H75" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="J75" t="n">
-        <v>-55.92</v>
+        <v>235.4</v>
       </c>
       <c r="K75" t="n">
-        <v>11249.88</v>
+        <v>16000.18</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46133.91666666666</v>
+        <v>46133.34375</v>
       </c>
       <c r="B76" s="1" t="n">
-        <v>46133.95833333334</v>
+        <v>46133.35416666666</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>BREAKOUT</t>
+          <t>BOUNCE</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4721.782</v>
+        <v>4787.023</v>
       </c>
       <c r="F76" t="n">
-        <v>4724.826</v>
+        <v>4784.259</v>
       </c>
       <c r="G76" t="n">
-        <v>4712.650000000001</v>
+        <v>4792.551</v>
       </c>
       <c r="H76" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="J76" t="n">
-        <v>-60.88</v>
+        <v>552.8</v>
       </c>
       <c r="K76" t="n">
-        <v>11189</v>
+        <v>16552.98</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46134.29166666666</v>
+        <v>46133.39583333334</v>
       </c>
       <c r="B77" s="1" t="n">
-        <v>46134.30208333334</v>
+        <v>46133.40625</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3570,80 +3570,80 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4765.742</v>
+        <v>4787.055</v>
       </c>
       <c r="F77" t="n">
-        <v>4766.742</v>
+        <v>4784.259</v>
       </c>
       <c r="G77" t="n">
-        <v>4762.742</v>
+        <v>4792.647000000001</v>
       </c>
       <c r="H77" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="J77" t="n">
-        <v>60</v>
+        <v>-279.6</v>
       </c>
       <c r="K77" t="n">
-        <v>11249</v>
+        <v>16273.38</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46134.63541666666</v>
+        <v>46133.91666666666</v>
       </c>
       <c r="B78" s="1" t="n">
-        <v>46134.64583333334</v>
+        <v>46133.94791666666</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>BOUNCE</t>
+          <t>BREAKOUT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4735.01</v>
+        <v>4721.782</v>
       </c>
       <c r="F78" t="n">
-        <v>4734.01</v>
+        <v>4724.826</v>
       </c>
       <c r="G78" t="n">
-        <v>4738.01</v>
+        <v>4715.694</v>
       </c>
       <c r="H78" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="J78" t="n">
-        <v>-20</v>
+        <v>608.8</v>
       </c>
       <c r="K78" t="n">
-        <v>11229</v>
+        <v>16882.18</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46134.80208333334</v>
+        <v>46134.29166666666</v>
       </c>
       <c r="B79" s="1" t="n">
-        <v>46134.8125</v>
+        <v>46134.30208333334</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3652,39 +3652,39 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4744.193</v>
+        <v>4765.742</v>
       </c>
       <c r="F79" t="n">
-        <v>4743.193</v>
+        <v>4766.742</v>
       </c>
       <c r="G79" t="n">
-        <v>4747.193</v>
+        <v>4763.742</v>
       </c>
       <c r="H79" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="J79" t="n">
-        <v>-20</v>
+        <v>200</v>
       </c>
       <c r="K79" t="n">
-        <v>11209</v>
+        <v>17082.18</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46135.33333333334</v>
+        <v>46134.63541666666</v>
       </c>
       <c r="B80" s="1" t="n">
-        <v>46135.34375</v>
+        <v>46134.64583333334</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3693,16 +3693,16 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4718.22</v>
+        <v>4735.01</v>
       </c>
       <c r="F80" t="n">
-        <v>4719.802</v>
+        <v>4734.01</v>
       </c>
       <c r="G80" t="n">
-        <v>4713.474000000002</v>
+        <v>4737.01</v>
       </c>
       <c r="H80" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -3710,22 +3710,22 @@
         </is>
       </c>
       <c r="J80" t="n">
-        <v>-31.64</v>
+        <v>-100</v>
       </c>
       <c r="K80" t="n">
-        <v>11177.36</v>
+        <v>16982.18</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46135.54166666666</v>
+        <v>46134.80208333334</v>
       </c>
       <c r="B81" s="1" t="n">
-        <v>46135.55208333334</v>
+        <v>46134.8125</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3734,16 +3734,16 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4725.761</v>
+        <v>4744.193</v>
       </c>
       <c r="F81" t="n">
-        <v>4726.761</v>
+        <v>4743.193</v>
       </c>
       <c r="G81" t="n">
-        <v>4722.761</v>
+        <v>4746.193</v>
       </c>
       <c r="H81" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -3751,18 +3751,18 @@
         </is>
       </c>
       <c r="J81" t="n">
-        <v>-20</v>
+        <v>-100</v>
       </c>
       <c r="K81" t="n">
-        <v>11157.36</v>
+        <v>16882.18</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46136.76041666666</v>
+        <v>46135.33333333334</v>
       </c>
       <c r="B82" s="1" t="n">
-        <v>46136.77083333334</v>
+        <v>46135.34375</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -3775,39 +3775,39 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4717.151</v>
+        <v>4718.22</v>
       </c>
       <c r="F82" t="n">
-        <v>4718.719</v>
+        <v>4719.802</v>
       </c>
       <c r="G82" t="n">
-        <v>4712.446999999999</v>
+        <v>4715.056000000001</v>
       </c>
       <c r="H82" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="J82" t="n">
-        <v>-31.36</v>
+        <v>316.4</v>
       </c>
       <c r="K82" t="n">
-        <v>11126</v>
+        <v>17198.58</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46139</v>
+        <v>46135.54166666666</v>
       </c>
       <c r="B83" s="1" t="n">
-        <v>46139.01041666666</v>
+        <v>46135.55208333334</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3816,16 +3816,16 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4679.616</v>
+        <v>4725.761</v>
       </c>
       <c r="F83" t="n">
-        <v>4678.616</v>
+        <v>4726.761</v>
       </c>
       <c r="G83" t="n">
-        <v>4682.616</v>
+        <v>4723.761</v>
       </c>
       <c r="H83" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -3833,22 +3833,22 @@
         </is>
       </c>
       <c r="J83" t="n">
-        <v>-20</v>
+        <v>-100</v>
       </c>
       <c r="K83" t="n">
-        <v>11106</v>
+        <v>17098.58</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46139.02083333334</v>
+        <v>46136.76041666666</v>
       </c>
       <c r="B84" s="1" t="n">
-        <v>46139.03125</v>
+        <v>46136.77083333334</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3857,76 +3857,76 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4680.504</v>
+        <v>4717.151</v>
       </c>
       <c r="F84" t="n">
-        <v>4678.66</v>
+        <v>4718.719</v>
       </c>
       <c r="G84" t="n">
-        <v>4686.036</v>
+        <v>4714.014999999999</v>
       </c>
       <c r="H84" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="J84" t="n">
-        <v>110.64</v>
+        <v>-156.8</v>
       </c>
       <c r="K84" t="n">
-        <v>11216.64</v>
+        <v>16941.78</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46139.04166666666</v>
+        <v>46139</v>
       </c>
       <c r="B85" s="1" t="n">
-        <v>46139.05208333334</v>
+        <v>46139.01041666666</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>BREAKOUT</t>
+          <t>BOUNCE</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4692.953</v>
+        <v>4679.616</v>
       </c>
       <c r="F85" t="n">
-        <v>4694.209000000001</v>
+        <v>4678.616</v>
       </c>
       <c r="G85" t="n">
-        <v>4689.184999999999</v>
+        <v>4681.616</v>
       </c>
       <c r="H85" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="J85" t="n">
-        <v>-25.12</v>
+        <v>200</v>
       </c>
       <c r="K85" t="n">
-        <v>11191.52</v>
+        <v>17141.78</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46139.35416666666</v>
+        <v>46139.02083333334</v>
       </c>
       <c r="B86" s="1" t="n">
-        <v>46139.36458333334</v>
+        <v>46139.03125</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -3935,39 +3935,39 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>BREAKOUT</t>
+          <t>BOUNCE</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4711.659</v>
+        <v>4680.504</v>
       </c>
       <c r="F86" t="n">
-        <v>4708.27</v>
+        <v>4678.66</v>
       </c>
       <c r="G86" t="n">
-        <v>4721.825999999997</v>
+        <v>4684.192</v>
       </c>
       <c r="H86" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="J86" t="n">
-        <v>-67.78</v>
+        <v>368.8</v>
       </c>
       <c r="K86" t="n">
-        <v>11123.74</v>
+        <v>17510.58</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46140.84375</v>
+        <v>46139.04166666666</v>
       </c>
       <c r="B87" s="1" t="n">
-        <v>46140.85416666666</v>
+        <v>46139.05208333334</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -3976,20 +3976,20 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>BOUNCE</t>
+          <t>BREAKOUT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4592.926</v>
+        <v>4692.953</v>
       </c>
       <c r="F87" t="n">
-        <v>4594.133</v>
+        <v>4694.209000000001</v>
       </c>
       <c r="G87" t="n">
-        <v>4589.305000000002</v>
+        <v>4690.441</v>
       </c>
       <c r="H87" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -3997,40 +3997,40 @@
         </is>
       </c>
       <c r="J87" t="n">
-        <v>-24.14</v>
+        <v>-125.6</v>
       </c>
       <c r="K87" t="n">
-        <v>11099.6</v>
+        <v>17384.98</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46141.1875</v>
+        <v>46139.35416666666</v>
       </c>
       <c r="B88" s="1" t="n">
-        <v>46141.19791666666</v>
+        <v>46139.36458333334</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>BOUNCE</t>
+          <t>BREAKOUT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4602.058</v>
+        <v>4711.659</v>
       </c>
       <c r="F88" t="n">
-        <v>4603.058</v>
+        <v>4708.27</v>
       </c>
       <c r="G88" t="n">
-        <v>4599.058</v>
+        <v>4718.436999999998</v>
       </c>
       <c r="H88" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -4038,22 +4038,22 @@
         </is>
       </c>
       <c r="J88" t="n">
-        <v>-20</v>
+        <v>-338.9</v>
       </c>
       <c r="K88" t="n">
-        <v>11079.6</v>
+        <v>17046.08</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46141.52083333334</v>
+        <v>46140.84375</v>
       </c>
       <c r="B89" s="1" t="n">
-        <v>46141.53125</v>
+        <v>46140.85416666666</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4062,16 +4062,16 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4557.49</v>
+        <v>4592.926</v>
       </c>
       <c r="F89" t="n">
-        <v>4555.675</v>
+        <v>4594.133</v>
       </c>
       <c r="G89" t="n">
-        <v>4562.934999999999</v>
+        <v>4590.512000000002</v>
       </c>
       <c r="H89" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -4079,40 +4079,40 @@
         </is>
       </c>
       <c r="J89" t="n">
-        <v>-36.3</v>
+        <v>-120.7</v>
       </c>
       <c r="K89" t="n">
-        <v>11043.3</v>
+        <v>16925.38</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46142.16666666666</v>
+        <v>46141.1875</v>
       </c>
       <c r="B90" s="1" t="n">
-        <v>46142.17708333334</v>
+        <v>46141.19791666666</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>BREAKOUT</t>
+          <t>BOUNCE</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4555.249</v>
+        <v>4602.058</v>
       </c>
       <c r="F90" t="n">
-        <v>4552.887</v>
+        <v>4603.058</v>
       </c>
       <c r="G90" t="n">
-        <v>4562.335</v>
+        <v>4600.058</v>
       </c>
       <c r="H90" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -4120,22 +4120,22 @@
         </is>
       </c>
       <c r="J90" t="n">
-        <v>-47.24</v>
+        <v>-100</v>
       </c>
       <c r="K90" t="n">
-        <v>10996.06</v>
+        <v>16825.38</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46142.48958333334</v>
+        <v>46141.52083333334</v>
       </c>
       <c r="B91" s="1" t="n">
-        <v>46142.5</v>
+        <v>46141.53125</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4144,16 +4144,16 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4629.938</v>
+        <v>4557.49</v>
       </c>
       <c r="F91" t="n">
-        <v>4631.21</v>
+        <v>4555.675</v>
       </c>
       <c r="G91" t="n">
-        <v>4626.122</v>
+        <v>4561.119999999999</v>
       </c>
       <c r="H91" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -4161,59 +4161,59 @@
         </is>
       </c>
       <c r="J91" t="n">
-        <v>-25.44</v>
+        <v>-181.5</v>
       </c>
       <c r="K91" t="n">
-        <v>10970.62</v>
+        <v>16643.88</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46142.51041666666</v>
+        <v>46142.16666666666</v>
       </c>
       <c r="B92" s="1" t="n">
-        <v>46142.52083333334</v>
+        <v>46142.17708333334</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>BOUNCE</t>
+          <t>BREAKOUT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4629.743</v>
+        <v>4555.249</v>
       </c>
       <c r="F92" t="n">
-        <v>4631.21</v>
+        <v>4552.887</v>
       </c>
       <c r="G92" t="n">
-        <v>4625.342000000001</v>
+        <v>4559.973</v>
       </c>
       <c r="H92" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="J92" t="n">
-        <v>88.02</v>
+        <v>-236.2</v>
       </c>
       <c r="K92" t="n">
-        <v>11058.64</v>
+        <v>16407.68</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46142.97916666666</v>
+        <v>46142.48958333334</v>
       </c>
       <c r="B93" s="1" t="n">
-        <v>46143</v>
+        <v>46142.5</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -4226,35 +4226,35 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4631.366</v>
+        <v>4629.938</v>
       </c>
       <c r="F93" t="n">
-        <v>4634.25</v>
+        <v>4631.21</v>
       </c>
       <c r="G93" t="n">
-        <v>4622.714</v>
+        <v>4627.394</v>
       </c>
       <c r="H93" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="J93" t="n">
-        <v>173.04</v>
+        <v>-127.2</v>
       </c>
       <c r="K93" t="n">
-        <v>11231.68</v>
+        <v>16280.48</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46143.14583333334</v>
+        <v>46142.51041666666</v>
       </c>
       <c r="B94" s="1" t="n">
-        <v>46143.15625</v>
+        <v>46142.52083333334</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -4267,39 +4267,39 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4626.273</v>
+        <v>4629.743</v>
       </c>
       <c r="F94" t="n">
-        <v>4627.273</v>
+        <v>4631.21</v>
       </c>
       <c r="G94" t="n">
-        <v>4623.273</v>
+        <v>4626.809000000001</v>
       </c>
       <c r="H94" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="J94" t="n">
-        <v>-20</v>
+        <v>293.4</v>
       </c>
       <c r="K94" t="n">
-        <v>11211.68</v>
+        <v>16573.88</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46143.20833333334</v>
+        <v>46142.97916666666</v>
       </c>
       <c r="B95" s="1" t="n">
-        <v>46143.21875</v>
+        <v>46143</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4308,39 +4308,39 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4614.105</v>
+        <v>4631.366</v>
       </c>
       <c r="F95" t="n">
-        <v>4612.942</v>
+        <v>4634.25</v>
       </c>
       <c r="G95" t="n">
-        <v>4617.593999999998</v>
+        <v>4625.598</v>
       </c>
       <c r="H95" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="J95" t="n">
-        <v>-23.26</v>
+        <v>576.8</v>
       </c>
       <c r="K95" t="n">
-        <v>11188.42</v>
+        <v>17150.68</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46143.5625</v>
+        <v>46143.14583333334</v>
       </c>
       <c r="B96" s="1" t="n">
-        <v>46143.57291666666</v>
+        <v>46143.15625</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4349,35 +4349,35 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4607.756</v>
+        <v>4626.273</v>
       </c>
       <c r="F96" t="n">
-        <v>4605.877</v>
+        <v>4627.273</v>
       </c>
       <c r="G96" t="n">
-        <v>4613.393</v>
+        <v>4624.273</v>
       </c>
       <c r="H96" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="J96" t="n">
-        <v>112.74</v>
+        <v>-100</v>
       </c>
       <c r="K96" t="n">
-        <v>11301.16</v>
+        <v>17050.68</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46146.0625</v>
+        <v>46143.20833333334</v>
       </c>
       <c r="B97" s="1" t="n">
-        <v>46146.07291666666</v>
+        <v>46143.21875</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -4390,35 +4390,35 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4601.471</v>
+        <v>4614.105</v>
       </c>
       <c r="F97" t="n">
-        <v>4600.009</v>
+        <v>4612.942</v>
       </c>
       <c r="G97" t="n">
-        <v>4605.856999999998</v>
+        <v>4616.430999999999</v>
       </c>
       <c r="H97" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="J97" t="n">
-        <v>87.72</v>
+        <v>-116.3</v>
       </c>
       <c r="K97" t="n">
-        <v>11388.88</v>
+        <v>16934.38</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46146.22916666666</v>
+        <v>46143.5625</v>
       </c>
       <c r="B98" s="1" t="n">
-        <v>46146.23958333334</v>
+        <v>46143.57291666666</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -4431,35 +4431,35 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4598.743</v>
+        <v>4607.756</v>
       </c>
       <c r="F98" t="n">
-        <v>4596.849</v>
+        <v>4605.877</v>
       </c>
       <c r="G98" t="n">
-        <v>4604.425000000001</v>
+        <v>4611.514</v>
       </c>
       <c r="H98" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="J98" t="n">
-        <v>-37.88</v>
+        <v>375.8</v>
       </c>
       <c r="K98" t="n">
-        <v>11351</v>
+        <v>17310.18</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46146.25</v>
+        <v>46146.0625</v>
       </c>
       <c r="B99" s="1" t="n">
-        <v>46146.26041666666</v>
+        <v>46146.07291666666</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -4472,98 +4472,98 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4597.291</v>
+        <v>4601.471</v>
       </c>
       <c r="F99" t="n">
-        <v>4596.291</v>
+        <v>4600.009</v>
       </c>
       <c r="G99" t="n">
-        <v>4600.291</v>
+        <v>4604.394999999999</v>
       </c>
       <c r="H99" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="J99" t="n">
-        <v>-20</v>
+        <v>292.4</v>
       </c>
       <c r="K99" t="n">
-        <v>11331</v>
+        <v>17602.58</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46146.60416666666</v>
+        <v>46146.22916666666</v>
       </c>
       <c r="B100" s="1" t="n">
-        <v>46146.61458333334</v>
+        <v>46146.23958333334</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>BREAKOUT</t>
+          <t>BOUNCE</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4574.587</v>
+        <v>4598.743</v>
       </c>
       <c r="F100" t="n">
-        <v>4575.587</v>
+        <v>4596.849</v>
       </c>
       <c r="G100" t="n">
-        <v>4571.587</v>
+        <v>4602.531000000001</v>
       </c>
       <c r="H100" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="J100" t="n">
-        <v>60</v>
+        <v>-189.4</v>
       </c>
       <c r="K100" t="n">
-        <v>11391</v>
+        <v>17413.18</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46146.71875</v>
+        <v>46146.25</v>
       </c>
       <c r="B101" s="1" t="n">
-        <v>46146.72916666666</v>
+        <v>46146.26041666666</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>BREAKOUT</t>
+          <t>BOUNCE</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4524.196</v>
+        <v>4597.291</v>
       </c>
       <c r="F101" t="n">
-        <v>4527.215</v>
+        <v>4596.291</v>
       </c>
       <c r="G101" t="n">
-        <v>4515.138999999999</v>
+        <v>4599.291</v>
       </c>
       <c r="H101" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -4571,18 +4571,18 @@
         </is>
       </c>
       <c r="J101" t="n">
-        <v>-60.38</v>
+        <v>-100</v>
       </c>
       <c r="K101" t="n">
-        <v>11330.62</v>
+        <v>17313.18</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46147.3125</v>
+        <v>46146.60416666666</v>
       </c>
       <c r="B102" s="1" t="n">
-        <v>46147.32291666666</v>
+        <v>46146.61458333334</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -4591,20 +4591,20 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>BOUNCE</t>
+          <t>BREAKOUT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>4551.301</v>
+        <v>4574.587</v>
       </c>
       <c r="F102" t="n">
-        <v>4553.69</v>
+        <v>4575.587</v>
       </c>
       <c r="G102" t="n">
-        <v>4544.134000000003</v>
+        <v>4572.587</v>
       </c>
       <c r="H102" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -4612,18 +4612,18 @@
         </is>
       </c>
       <c r="J102" t="n">
-        <v>143.34</v>
+        <v>200</v>
       </c>
       <c r="K102" t="n">
-        <v>11473.96</v>
+        <v>17513.18</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46149.64583333334</v>
+        <v>46146.71875</v>
       </c>
       <c r="B103" s="1" t="n">
-        <v>46149.65625</v>
+        <v>46146.72916666666</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -4632,39 +4632,39 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>BOUNCE</t>
+          <t>BREAKOUT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>4738.742</v>
+        <v>4524.196</v>
       </c>
       <c r="F103" t="n">
-        <v>4740.759</v>
+        <v>4527.215</v>
       </c>
       <c r="G103" t="n">
-        <v>4732.691000000001</v>
+        <v>4518.157999999999</v>
       </c>
       <c r="H103" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="J103" t="n">
-        <v>121.02</v>
+        <v>-301.9</v>
       </c>
       <c r="K103" t="n">
-        <v>11594.98</v>
+        <v>17211.28</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46150</v>
+        <v>46147.3125</v>
       </c>
       <c r="B104" s="1" t="n">
-        <v>46150.02083333334</v>
+        <v>46147.32291666666</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -4673,39 +4673,39 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>BREAKOUT</t>
+          <t>BOUNCE</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4702.594</v>
+        <v>4551.301</v>
       </c>
       <c r="F104" t="n">
-        <v>4705.789</v>
+        <v>4553.69</v>
       </c>
       <c r="G104" t="n">
-        <v>4693.009000000001</v>
+        <v>4546.523000000002</v>
       </c>
       <c r="H104" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="J104" t="n">
-        <v>-63.9</v>
+        <v>477.8</v>
       </c>
       <c r="K104" t="n">
-        <v>11531.08</v>
+        <v>17689.08</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46150.15625</v>
+        <v>46149.64583333334</v>
       </c>
       <c r="B105" s="1" t="n">
-        <v>46150.16666666666</v>
+        <v>46149.65625</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -4718,16 +4718,16 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4719.697</v>
+        <v>4738.742</v>
       </c>
       <c r="F105" t="n">
-        <v>4720.782</v>
+        <v>4740.759</v>
       </c>
       <c r="G105" t="n">
-        <v>4716.442</v>
+        <v>4734.708000000001</v>
       </c>
       <c r="H105" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -4735,18 +4735,18 @@
         </is>
       </c>
       <c r="J105" t="n">
-        <v>65.09999999999999</v>
+        <v>403.4</v>
       </c>
       <c r="K105" t="n">
-        <v>11596.18</v>
+        <v>18092.48</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46150.32291666666</v>
+        <v>46150</v>
       </c>
       <c r="B106" s="1" t="n">
-        <v>46150.33333333334</v>
+        <v>46150.01041666666</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -4755,39 +4755,39 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>BOUNCE</t>
+          <t>BREAKOUT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>4708.033</v>
+        <v>4702.594</v>
       </c>
       <c r="F106" t="n">
-        <v>4710.934</v>
+        <v>4705.789</v>
       </c>
       <c r="G106" t="n">
-        <v>4699.330000000001</v>
+        <v>4696.204000000001</v>
       </c>
       <c r="H106" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="J106" t="n">
-        <v>-58.02</v>
+        <v>639</v>
       </c>
       <c r="K106" t="n">
-        <v>11538.16</v>
+        <v>18731.48</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46150.38541666666</v>
+        <v>46150.15625</v>
       </c>
       <c r="B107" s="1" t="n">
-        <v>46150.39583333334</v>
+        <v>46150.16666666666</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -4800,16 +4800,16 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>4717.994</v>
+        <v>4719.697</v>
       </c>
       <c r="F107" t="n">
         <v>4720.782</v>
       </c>
       <c r="G107" t="n">
-        <v>4709.629999999998</v>
+        <v>4717.527</v>
       </c>
       <c r="H107" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
@@ -4817,63 +4817,63 @@
         </is>
       </c>
       <c r="J107" t="n">
-        <v>167.28</v>
+        <v>217</v>
       </c>
       <c r="K107" t="n">
-        <v>11705.44</v>
+        <v>18948.48</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46150.40625</v>
+        <v>46150.32291666666</v>
       </c>
       <c r="B108" s="1" t="n">
-        <v>46150.42708333334</v>
+        <v>46150.33333333334</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>BREAKOUT</t>
+          <t>BOUNCE</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>4711.712</v>
+        <v>4708.033</v>
       </c>
       <c r="F108" t="n">
-        <v>4707.934</v>
+        <v>4710.934</v>
       </c>
       <c r="G108" t="n">
-        <v>4723.046000000001</v>
+        <v>4702.231000000001</v>
       </c>
       <c r="H108" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="J108" t="n">
-        <v>226.68</v>
+        <v>-290.1</v>
       </c>
       <c r="K108" t="n">
-        <v>11932.12</v>
+        <v>18658.38</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46153.48958333334</v>
+        <v>46150.38541666666</v>
       </c>
       <c r="B109" s="1" t="n">
-        <v>46153.5</v>
+        <v>46150.39583333334</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -4882,76 +4882,76 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>4674.327</v>
+        <v>4717.994</v>
       </c>
       <c r="F109" t="n">
-        <v>4673.294</v>
+        <v>4720.782</v>
       </c>
       <c r="G109" t="n">
-        <v>4677.426000000001</v>
+        <v>4712.417999999999</v>
       </c>
       <c r="H109" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="J109" t="n">
-        <v>-20.66</v>
+        <v>557.6</v>
       </c>
       <c r="K109" t="n">
-        <v>11911.46</v>
+        <v>19215.98</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46153.91666666666</v>
+        <v>46150.40625</v>
       </c>
       <c r="B110" s="1" t="n">
-        <v>46153.92708333334</v>
+        <v>46150.42708333334</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>BOUNCE</t>
+          <t>BREAKOUT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>4738.909</v>
+        <v>4711.712</v>
       </c>
       <c r="F110" t="n">
-        <v>4739.909</v>
+        <v>4707.934</v>
       </c>
       <c r="G110" t="n">
-        <v>4735.909</v>
+        <v>4719.268000000001</v>
       </c>
       <c r="H110" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="J110" t="n">
-        <v>-20</v>
+        <v>755.6</v>
       </c>
       <c r="K110" t="n">
-        <v>11891.46</v>
+        <v>19971.58</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46154.60416666666</v>
+        <v>46153.48958333334</v>
       </c>
       <c r="B111" s="1" t="n">
-        <v>46154.61458333334</v>
+        <v>46153.5</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -4964,16 +4964,16 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>4685.938</v>
+        <v>4674.327</v>
       </c>
       <c r="F111" t="n">
-        <v>4684.938</v>
+        <v>4673.294</v>
       </c>
       <c r="G111" t="n">
-        <v>4688.938</v>
+        <v>4676.393000000001</v>
       </c>
       <c r="H111" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
@@ -4981,18 +4981,18 @@
         </is>
       </c>
       <c r="J111" t="n">
-        <v>-20</v>
+        <v>-103.3</v>
       </c>
       <c r="K111" t="n">
-        <v>11871.46</v>
+        <v>19868.28</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46155.41666666666</v>
+        <v>46153.91666666666</v>
       </c>
       <c r="B112" s="1" t="n">
-        <v>46155.42708333334</v>
+        <v>46153.92708333334</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -5005,16 +5005,16 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>4702.409</v>
+        <v>4738.909</v>
       </c>
       <c r="F112" t="n">
-        <v>4704.15</v>
+        <v>4739.909</v>
       </c>
       <c r="G112" t="n">
-        <v>4697.186</v>
+        <v>4736.909</v>
       </c>
       <c r="H112" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
@@ -5022,18 +5022,18 @@
         </is>
       </c>
       <c r="J112" t="n">
-        <v>-34.82</v>
+        <v>-100</v>
       </c>
       <c r="K112" t="n">
-        <v>11836.64</v>
+        <v>19768.28</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46155.78125</v>
+        <v>46154.60416666666</v>
       </c>
       <c r="B113" s="1" t="n">
-        <v>46155.79166666666</v>
+        <v>46154.61458333334</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -5046,35 +5046,35 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>4684.757</v>
+        <v>4685.938</v>
       </c>
       <c r="F113" t="n">
-        <v>4683.757</v>
+        <v>4684.938</v>
       </c>
       <c r="G113" t="n">
-        <v>4687.757</v>
+        <v>4687.938</v>
       </c>
       <c r="H113" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="J113" t="n">
-        <v>60</v>
+        <v>-100</v>
       </c>
       <c r="K113" t="n">
-        <v>11896.64</v>
+        <v>19668.28</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46155.84375</v>
+        <v>46155.41666666666</v>
       </c>
       <c r="B114" s="1" t="n">
-        <v>46155.91666666666</v>
+        <v>46155.42708333334</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -5083,61 +5083,61 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>BREAKOUT</t>
+          <t>BOUNCE</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>4691.132</v>
+        <v>4702.409</v>
       </c>
       <c r="F114" t="n">
-        <v>4692.823</v>
+        <v>4704.15</v>
       </c>
       <c r="G114" t="n">
-        <v>4686.058999999997</v>
+        <v>4698.927</v>
       </c>
       <c r="H114" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="J114" t="n">
-        <v>-33.82</v>
+        <v>348.2</v>
       </c>
       <c r="K114" t="n">
-        <v>11862.82</v>
+        <v>20016.48</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46156.59375</v>
+        <v>46155.78125</v>
       </c>
       <c r="B115" s="1" t="n">
-        <v>46156.60416666666</v>
+        <v>46155.79166666666</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>BREAKOUT</t>
+          <t>BOUNCE</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>4691.28</v>
+        <v>4684.757</v>
       </c>
       <c r="F115" t="n">
-        <v>4692.28</v>
+        <v>4683.757</v>
       </c>
       <c r="G115" t="n">
-        <v>4688.28</v>
+        <v>4686.757</v>
       </c>
       <c r="H115" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
@@ -5145,40 +5145,40 @@
         </is>
       </c>
       <c r="J115" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="K115" t="n">
-        <v>11922.82</v>
+        <v>20216.48</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46157.51041666666</v>
+        <v>46155.84375</v>
       </c>
       <c r="B116" s="1" t="n">
-        <v>46157.52083333334</v>
+        <v>46155.91666666666</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>BOUNCE</t>
+          <t>BREAKOUT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>4555.162</v>
+        <v>4691.132</v>
       </c>
       <c r="F116" t="n">
-        <v>4554.162</v>
+        <v>4692.823</v>
       </c>
       <c r="G116" t="n">
-        <v>4558.162</v>
+        <v>4687.749999999998</v>
       </c>
       <c r="H116" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
@@ -5186,22 +5186,22 @@
         </is>
       </c>
       <c r="J116" t="n">
-        <v>-20</v>
+        <v>-169.1</v>
       </c>
       <c r="K116" t="n">
-        <v>11902.82</v>
+        <v>20047.38</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46157.77083333334</v>
+        <v>46156.59375</v>
       </c>
       <c r="B117" s="1" t="n">
-        <v>46157.78125</v>
+        <v>46156.60416666666</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -5210,16 +5210,16 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>4557.443</v>
+        <v>4691.28</v>
       </c>
       <c r="F117" t="n">
-        <v>4556.443</v>
+        <v>4692.28</v>
       </c>
       <c r="G117" t="n">
-        <v>4560.443</v>
+        <v>4689.28</v>
       </c>
       <c r="H117" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
@@ -5227,22 +5227,22 @@
         </is>
       </c>
       <c r="J117" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="K117" t="n">
-        <v>11962.82</v>
+        <v>20247.38</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46160.3125</v>
+        <v>46157.51041666666</v>
       </c>
       <c r="B118" s="1" t="n">
-        <v>46160.32291666666</v>
+        <v>46157.52083333334</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5251,57 +5251,57 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>4549.108</v>
+        <v>4555.162</v>
       </c>
       <c r="F118" t="n">
-        <v>4551.477</v>
+        <v>4554.162</v>
       </c>
       <c r="G118" t="n">
-        <v>4542.001000000001</v>
+        <v>4557.162</v>
       </c>
       <c r="H118" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="J118" t="n">
-        <v>142.14</v>
+        <v>-100</v>
       </c>
       <c r="K118" t="n">
-        <v>12104.96</v>
+        <v>20147.38</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46160.36458333334</v>
+        <v>46157.77083333334</v>
       </c>
       <c r="B119" s="1" t="n">
-        <v>46160.375</v>
+        <v>46157.78125</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>BOUNCE</t>
+          <t>BREAKOUT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>4550.047</v>
+        <v>4557.443</v>
       </c>
       <c r="F119" t="n">
-        <v>4551.477</v>
+        <v>4556.443</v>
       </c>
       <c r="G119" t="n">
-        <v>4545.756999999999</v>
+        <v>4559.443</v>
       </c>
       <c r="H119" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
@@ -5309,22 +5309,22 @@
         </is>
       </c>
       <c r="J119" t="n">
-        <v>85.8</v>
+        <v>200</v>
       </c>
       <c r="K119" t="n">
-        <v>12190.76</v>
+        <v>20347.38</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46160.45833333334</v>
+        <v>46160.3125</v>
       </c>
       <c r="B120" s="1" t="n">
-        <v>46160.46875</v>
+        <v>46160.32291666666</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -5333,35 +5333,35 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4539.363</v>
+        <v>4549.108</v>
       </c>
       <c r="F120" t="n">
-        <v>4536.941</v>
+        <v>4551.477</v>
       </c>
       <c r="G120" t="n">
-        <v>4546.629000000002</v>
+        <v>4544.370000000001</v>
       </c>
       <c r="H120" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="J120" t="n">
-        <v>-48.44</v>
+        <v>473.8</v>
       </c>
       <c r="K120" t="n">
-        <v>12142.32</v>
+        <v>20821.18</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46160.82291666666</v>
+        <v>46160.36458333334</v>
       </c>
       <c r="B121" s="1" t="n">
-        <v>46160.83333333334</v>
+        <v>46160.375</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -5374,35 +5374,35 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>4558.429</v>
+        <v>4550.047</v>
       </c>
       <c r="F121" t="n">
-        <v>4559.429</v>
+        <v>4551.477</v>
       </c>
       <c r="G121" t="n">
-        <v>4555.429</v>
+        <v>4547.186999999999</v>
       </c>
       <c r="H121" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="J121" t="n">
-        <v>-20</v>
+        <v>286</v>
       </c>
       <c r="K121" t="n">
-        <v>12122.32</v>
+        <v>21107.18</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46161.19791666666</v>
+        <v>46160.45833333334</v>
       </c>
       <c r="B122" s="1" t="n">
-        <v>46161.20833333334</v>
+        <v>46160.46875</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -5415,39 +5415,39 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>4542.255</v>
+        <v>4539.363</v>
       </c>
       <c r="F122" t="n">
-        <v>4541.255</v>
+        <v>4536.941</v>
       </c>
       <c r="G122" t="n">
-        <v>4545.255</v>
+        <v>4544.207000000001</v>
       </c>
       <c r="H122" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="J122" t="n">
-        <v>60</v>
+        <v>-242.2</v>
       </c>
       <c r="K122" t="n">
-        <v>12182.32</v>
+        <v>20864.98</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46161.51041666666</v>
+        <v>46160.82291666666</v>
       </c>
       <c r="B123" s="1" t="n">
-        <v>46161.52083333334</v>
+        <v>46160.83333333334</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -5456,16 +5456,16 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>4543.307</v>
+        <v>4558.429</v>
       </c>
       <c r="F123" t="n">
-        <v>4542.043</v>
+        <v>4559.429</v>
       </c>
       <c r="G123" t="n">
-        <v>4547.099</v>
+        <v>4556.429</v>
       </c>
       <c r="H123" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -5473,22 +5473,22 @@
         </is>
       </c>
       <c r="J123" t="n">
-        <v>-25.28</v>
+        <v>-100</v>
       </c>
       <c r="K123" t="n">
-        <v>12157.04</v>
+        <v>20764.98</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46162.53125</v>
+        <v>46161.19791666666</v>
       </c>
       <c r="B124" s="1" t="n">
-        <v>46162.54166666666</v>
+        <v>46161.20833333334</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -5497,39 +5497,39 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>4496.024</v>
+        <v>4542.255</v>
       </c>
       <c r="F124" t="n">
-        <v>4498.683</v>
+        <v>4541.255</v>
       </c>
       <c r="G124" t="n">
-        <v>4488.047000000001</v>
+        <v>4544.255</v>
       </c>
       <c r="H124" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="J124" t="n">
-        <v>-53.18</v>
+        <v>200</v>
       </c>
       <c r="K124" t="n">
-        <v>12103.86</v>
+        <v>20964.98</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46162.77083333334</v>
+        <v>46161.51041666666</v>
       </c>
       <c r="B125" s="1" t="n">
-        <v>46162.78125</v>
+        <v>46161.52083333334</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -5538,57 +5538,57 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>4537.104</v>
+        <v>4543.307</v>
       </c>
       <c r="F125" t="n">
-        <v>4539.78</v>
+        <v>4542.043</v>
       </c>
       <c r="G125" t="n">
-        <v>4529.076000000002</v>
+        <v>4545.835</v>
       </c>
       <c r="H125" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="J125" t="n">
-        <v>-53.52</v>
+        <v>252.8</v>
       </c>
       <c r="K125" t="n">
-        <v>12050.34</v>
+        <v>21217.78</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46162.92708333334</v>
+        <v>46162.53125</v>
       </c>
       <c r="B126" s="1" t="n">
-        <v>46162.96875</v>
+        <v>46162.54166666666</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>BREAKOUT</t>
+          <t>BOUNCE</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>4539.141</v>
+        <v>4496.024</v>
       </c>
       <c r="F126" t="n">
-        <v>4536.78</v>
+        <v>4498.683</v>
       </c>
       <c r="G126" t="n">
-        <v>4546.223999999999</v>
+        <v>4490.706000000001</v>
       </c>
       <c r="H126" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
@@ -5596,22 +5596,22 @@
         </is>
       </c>
       <c r="J126" t="n">
-        <v>-47.22</v>
+        <v>-265.9</v>
       </c>
       <c r="K126" t="n">
-        <v>12003.12</v>
+        <v>20951.88</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46163.4375</v>
+        <v>46162.77083333334</v>
       </c>
       <c r="B127" s="1" t="n">
-        <v>46163.44791666666</v>
+        <v>46162.78125</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -5620,16 +5620,16 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>4516.922</v>
+        <v>4537.104</v>
       </c>
       <c r="F127" t="n">
-        <v>4515.922</v>
+        <v>4539.78</v>
       </c>
       <c r="G127" t="n">
-        <v>4519.922</v>
+        <v>4531.752000000001</v>
       </c>
       <c r="H127" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
@@ -5637,18 +5637,18 @@
         </is>
       </c>
       <c r="J127" t="n">
-        <v>-20</v>
+        <v>-267.6</v>
       </c>
       <c r="K127" t="n">
-        <v>11983.12</v>
+        <v>20684.28</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46163.59375</v>
+        <v>46162.92708333334</v>
       </c>
       <c r="B128" s="1" t="n">
-        <v>46163.60416666666</v>
+        <v>46162.94791666666</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -5657,20 +5657,20 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>BOUNCE</t>
+          <t>BREAKOUT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>4507.284</v>
+        <v>4539.141</v>
       </c>
       <c r="F128" t="n">
-        <v>4506.284</v>
+        <v>4536.78</v>
       </c>
       <c r="G128" t="n">
-        <v>4510.284</v>
+        <v>4543.862999999999</v>
       </c>
       <c r="H128" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
@@ -5678,18 +5678,18 @@
         </is>
       </c>
       <c r="J128" t="n">
-        <v>60</v>
+        <v>472.2</v>
       </c>
       <c r="K128" t="n">
-        <v>12043.12</v>
+        <v>21156.48</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46164.01041666666</v>
+        <v>46163.4375</v>
       </c>
       <c r="B129" s="1" t="n">
-        <v>46164.03125</v>
+        <v>46163.44791666666</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -5702,16 +5702,16 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>4536.073</v>
+        <v>4516.922</v>
       </c>
       <c r="F129" t="n">
-        <v>4533.314</v>
+        <v>4515.922</v>
       </c>
       <c r="G129" t="n">
-        <v>4544.35</v>
+        <v>4518.922</v>
       </c>
       <c r="H129" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
@@ -5719,18 +5719,18 @@
         </is>
       </c>
       <c r="J129" t="n">
-        <v>-55.18</v>
+        <v>-100</v>
       </c>
       <c r="K129" t="n">
-        <v>11987.94</v>
+        <v>21056.48</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46164.10416666666</v>
+        <v>46163.59375</v>
       </c>
       <c r="B130" s="1" t="n">
-        <v>46164.11458333334</v>
+        <v>46163.60416666666</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -5739,39 +5739,39 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>BREAKOUT</t>
+          <t>BOUNCE</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>4522.717</v>
+        <v>4507.284</v>
       </c>
       <c r="F130" t="n">
-        <v>4519.633</v>
+        <v>4506.284</v>
       </c>
       <c r="G130" t="n">
-        <v>4531.968999999999</v>
+        <v>4509.284</v>
       </c>
       <c r="H130" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="J130" t="n">
-        <v>-61.68</v>
+        <v>200</v>
       </c>
       <c r="K130" t="n">
-        <v>11926.26</v>
+        <v>21256.48</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46164.47916666666</v>
+        <v>46164.01041666666</v>
       </c>
       <c r="B131" s="1" t="n">
-        <v>46164.5</v>
+        <v>46164.03125</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -5784,35 +5784,35 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>4521.543</v>
+        <v>4536.073</v>
       </c>
       <c r="F131" t="n">
-        <v>4519.324</v>
+        <v>4533.314</v>
       </c>
       <c r="G131" t="n">
-        <v>4528.2</v>
+        <v>4541.591</v>
       </c>
       <c r="H131" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="J131" t="n">
-        <v>133.14</v>
+        <v>-275.9</v>
       </c>
       <c r="K131" t="n">
-        <v>12059.4</v>
+        <v>20980.58</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46164.78125</v>
+        <v>46164.10416666666</v>
       </c>
       <c r="B132" s="1" t="n">
-        <v>46164.79166666666</v>
+        <v>46164.11458333334</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -5821,20 +5821,20 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>BOUNCE</t>
+          <t>BREAKOUT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>4515.193</v>
+        <v>4522.717</v>
       </c>
       <c r="F132" t="n">
-        <v>4514.193</v>
+        <v>4519.633</v>
       </c>
       <c r="G132" t="n">
-        <v>4518.193</v>
+        <v>4528.884999999999</v>
       </c>
       <c r="H132" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
@@ -5842,18 +5842,18 @@
         </is>
       </c>
       <c r="J132" t="n">
-        <v>-20</v>
+        <v>-308.4</v>
       </c>
       <c r="K132" t="n">
-        <v>12039.4</v>
+        <v>20672.18</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46164.84375</v>
+        <v>46164.47916666666</v>
       </c>
       <c r="B133" s="1" t="n">
-        <v>46164.85416666666</v>
+        <v>46164.5</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -5866,39 +5866,39 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>4509.975</v>
+        <v>4521.543</v>
       </c>
       <c r="F133" t="n">
-        <v>4508.619</v>
+        <v>4519.324</v>
       </c>
       <c r="G133" t="n">
-        <v>4514.043000000002</v>
+        <v>4525.981</v>
       </c>
       <c r="H133" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="J133" t="n">
-        <v>-27.12</v>
+        <v>443.8</v>
       </c>
       <c r="K133" t="n">
-        <v>12012.28</v>
+        <v>21115.98</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46167.70833333334</v>
+        <v>46164.78125</v>
       </c>
       <c r="B134" s="1" t="n">
-        <v>46167.71875</v>
+        <v>46164.79166666666</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -5907,39 +5907,39 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4574.134</v>
+        <v>4515.193</v>
       </c>
       <c r="F134" t="n">
-        <v>4575.134</v>
+        <v>4514.193</v>
       </c>
       <c r="G134" t="n">
-        <v>4571.134</v>
+        <v>4517.193</v>
       </c>
       <c r="H134" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="J134" t="n">
-        <v>60</v>
+        <v>-100</v>
       </c>
       <c r="K134" t="n">
-        <v>12072.28</v>
+        <v>21015.98</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46167.92708333334</v>
+        <v>46164.84375</v>
       </c>
       <c r="B135" s="1" t="n">
-        <v>46167.94791666666</v>
+        <v>46164.85416666666</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -5948,16 +5948,16 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>4572.911</v>
+        <v>4509.975</v>
       </c>
       <c r="F135" t="n">
-        <v>4575.128</v>
+        <v>4508.619</v>
       </c>
       <c r="G135" t="n">
-        <v>4566.260000000001</v>
+        <v>4512.687000000002</v>
       </c>
       <c r="H135" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
@@ -5965,18 +5965,18 @@
         </is>
       </c>
       <c r="J135" t="n">
-        <v>-44.34</v>
+        <v>-135.6</v>
       </c>
       <c r="K135" t="n">
-        <v>12027.94</v>
+        <v>20880.38</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46168.14583333334</v>
+        <v>46167.70833333334</v>
       </c>
       <c r="B136" s="1" t="n">
-        <v>46168.15625</v>
+        <v>46167.71875</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -5985,39 +5985,39 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>BREAKOUT</t>
+          <t>BOUNCE</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>4541.547</v>
+        <v>4574.134</v>
       </c>
       <c r="F136" t="n">
-        <v>4542.547</v>
+        <v>4575.134</v>
       </c>
       <c r="G136" t="n">
-        <v>4538.547</v>
+        <v>4572.134</v>
       </c>
       <c r="H136" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="J136" t="n">
-        <v>-20</v>
+        <v>200</v>
       </c>
       <c r="K136" t="n">
-        <v>12007.94</v>
+        <v>21080.38</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46168.44791666666</v>
+        <v>46167.92708333334</v>
       </c>
       <c r="B137" s="1" t="n">
-        <v>46168.46875</v>
+        <v>46167.94791666666</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -6030,57 +6030,57 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>4534.564</v>
+        <v>4572.911</v>
       </c>
       <c r="F137" t="n">
-        <v>4536.459</v>
+        <v>4575.128</v>
       </c>
       <c r="G137" t="n">
-        <v>4528.879000000002</v>
+        <v>4568.477000000001</v>
       </c>
       <c r="H137" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="J137" t="n">
-        <v>113.7</v>
+        <v>-221.7</v>
       </c>
       <c r="K137" t="n">
-        <v>12121.64</v>
+        <v>20858.68</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46168.67708333334</v>
+        <v>46168.14583333334</v>
       </c>
       <c r="B138" s="1" t="n">
-        <v>46168.6875</v>
+        <v>46168.15625</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>BOUNCE</t>
+          <t>BREAKOUT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4507.745</v>
+        <v>4541.547</v>
       </c>
       <c r="F138" t="n">
-        <v>4506.214</v>
+        <v>4542.547</v>
       </c>
       <c r="G138" t="n">
-        <v>4512.338</v>
+        <v>4539.547</v>
       </c>
       <c r="H138" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
@@ -6088,18 +6088,18 @@
         </is>
       </c>
       <c r="J138" t="n">
-        <v>-30.62</v>
+        <v>-100</v>
       </c>
       <c r="K138" t="n">
-        <v>12091.02</v>
+        <v>20758.68</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46169.19791666666</v>
+        <v>46168.44791666666</v>
       </c>
       <c r="B139" s="1" t="n">
-        <v>46169.20833333334</v>
+        <v>46168.46875</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -6112,39 +6112,39 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4510.335</v>
+        <v>4534.564</v>
       </c>
       <c r="F139" t="n">
-        <v>4512.215</v>
+        <v>4536.459</v>
       </c>
       <c r="G139" t="n">
-        <v>4504.695</v>
+        <v>4530.774000000001</v>
       </c>
       <c r="H139" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="J139" t="n">
-        <v>-37.6</v>
+        <v>379</v>
       </c>
       <c r="K139" t="n">
-        <v>12053.42</v>
+        <v>21137.68</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46169.84375</v>
+        <v>46168.67708333334</v>
       </c>
       <c r="B140" s="1" t="n">
-        <v>46169.91666666666</v>
+        <v>46168.6875</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -6153,35 +6153,35 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>4455.093</v>
+        <v>4507.745</v>
       </c>
       <c r="F140" t="n">
-        <v>4456.992</v>
+        <v>4506.214</v>
       </c>
       <c r="G140" t="n">
-        <v>4449.395999999999</v>
+        <v>4510.807</v>
       </c>
       <c r="H140" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="J140" t="n">
-        <v>-37.98</v>
+        <v>306.2</v>
       </c>
       <c r="K140" t="n">
-        <v>12015.44</v>
+        <v>21443.88</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46171.16666666666</v>
+        <v>46169.19791666666</v>
       </c>
       <c r="B141" s="1" t="n">
-        <v>46171.17708333334</v>
+        <v>46169.20833333334</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -6190,20 +6190,20 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>BREAKOUT</t>
+          <t>BOUNCE</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>4502.198</v>
+        <v>4510.335</v>
       </c>
       <c r="F141" t="n">
-        <v>4503.198</v>
+        <v>4512.215</v>
       </c>
       <c r="G141" t="n">
-        <v>4499.198</v>
+        <v>4506.575</v>
       </c>
       <c r="H141" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
@@ -6211,18 +6211,18 @@
         </is>
       </c>
       <c r="J141" t="n">
-        <v>-20</v>
+        <v>-188</v>
       </c>
       <c r="K141" t="n">
-        <v>11995.44</v>
+        <v>21255.88</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46171.29166666666</v>
+        <v>46169.84375</v>
       </c>
       <c r="B142" s="1" t="n">
-        <v>46171.30208333334</v>
+        <v>46169.91666666666</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -6235,39 +6235,39 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>4516.425</v>
+        <v>4455.093</v>
       </c>
       <c r="F142" t="n">
-        <v>4518.088</v>
+        <v>4456.992</v>
       </c>
       <c r="G142" t="n">
-        <v>4511.436000000002</v>
+        <v>4451.294999999999</v>
       </c>
       <c r="H142" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="J142" t="n">
-        <v>99.78</v>
+        <v>-189.9</v>
       </c>
       <c r="K142" t="n">
-        <v>12095.22</v>
+        <v>21065.98</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46171.53125</v>
+        <v>46171.16666666666</v>
       </c>
       <c r="B143" s="1" t="n">
-        <v>46171.54166666666</v>
+        <v>46171.17708333334</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -6276,16 +6276,16 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>4522.843</v>
+        <v>4502.198</v>
       </c>
       <c r="F143" t="n">
-        <v>4519.299</v>
+        <v>4503.198</v>
       </c>
       <c r="G143" t="n">
-        <v>4533.474999999999</v>
+        <v>4500.198</v>
       </c>
       <c r="H143" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
@@ -6293,22 +6293,22 @@
         </is>
       </c>
       <c r="J143" t="n">
-        <v>-70.88</v>
+        <v>-100</v>
       </c>
       <c r="K143" t="n">
-        <v>12024.34</v>
+        <v>20965.98</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46171.79166666666</v>
+        <v>46171.29166666666</v>
       </c>
       <c r="B144" s="1" t="n">
-        <v>46171.80208333334</v>
+        <v>46171.30208333334</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -6317,35 +6317,35 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>4558.357</v>
+        <v>4516.425</v>
       </c>
       <c r="F144" t="n">
-        <v>4556.219</v>
+        <v>4518.088</v>
       </c>
       <c r="G144" t="n">
-        <v>4564.771</v>
+        <v>4513.099000000001</v>
       </c>
       <c r="H144" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="J144" t="n">
-        <v>-42.76</v>
+        <v>332.6</v>
       </c>
       <c r="K144" t="n">
-        <v>11981.58</v>
+        <v>21298.58</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46174.22916666666</v>
+        <v>46171.53125</v>
       </c>
       <c r="B145" s="1" t="n">
-        <v>46174.25</v>
+        <v>46171.54166666666</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -6354,20 +6354,20 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>BOUNCE</t>
+          <t>BREAKOUT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>4519.644</v>
+        <v>4522.843</v>
       </c>
       <c r="F145" t="n">
-        <v>4516.854</v>
+        <v>4519.299</v>
       </c>
       <c r="G145" t="n">
-        <v>4528.014</v>
+        <v>4529.931</v>
       </c>
       <c r="H145" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
@@ -6375,18 +6375,18 @@
         </is>
       </c>
       <c r="J145" t="n">
-        <v>-55.8</v>
+        <v>-354.4</v>
       </c>
       <c r="K145" t="n">
-        <v>11925.78</v>
+        <v>20944.18</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46174.41666666666</v>
+        <v>46171.79166666666</v>
       </c>
       <c r="B146" s="1" t="n">
-        <v>46174.42708333334</v>
+        <v>46171.80208333334</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -6399,16 +6399,16 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>4501.323</v>
+        <v>4558.357</v>
       </c>
       <c r="F146" t="n">
-        <v>4498.514</v>
+        <v>4556.219</v>
       </c>
       <c r="G146" t="n">
-        <v>4509.750000000001</v>
+        <v>4562.633</v>
       </c>
       <c r="H146" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
@@ -6416,22 +6416,22 @@
         </is>
       </c>
       <c r="J146" t="n">
-        <v>-56.18</v>
+        <v>-213.8</v>
       </c>
       <c r="K146" t="n">
-        <v>11869.6</v>
+        <v>20730.38</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46175.125</v>
+        <v>46174.22916666666</v>
       </c>
       <c r="B147" s="1" t="n">
-        <v>46175.13541666666</v>
+        <v>46174.25</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -6440,16 +6440,16 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4488.012</v>
+        <v>4519.644</v>
       </c>
       <c r="F147" t="n">
-        <v>4489.012</v>
+        <v>4516.854</v>
       </c>
       <c r="G147" t="n">
-        <v>4485.012</v>
+        <v>4525.224</v>
       </c>
       <c r="H147" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
@@ -6457,22 +6457,22 @@
         </is>
       </c>
       <c r="J147" t="n">
-        <v>-20</v>
+        <v>-279</v>
       </c>
       <c r="K147" t="n">
-        <v>11849.6</v>
+        <v>20451.38</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46175.38541666666</v>
+        <v>46174.41666666666</v>
       </c>
       <c r="B148" s="1" t="n">
-        <v>46175.40625</v>
+        <v>46174.42708333334</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -6481,16 +6481,16 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>4526.834</v>
+        <v>4501.323</v>
       </c>
       <c r="F148" t="n">
-        <v>4529.791</v>
+        <v>4498.514</v>
       </c>
       <c r="G148" t="n">
-        <v>4517.962999999999</v>
+        <v>4506.941000000001</v>
       </c>
       <c r="H148" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
@@ -6498,22 +6498,22 @@
         </is>
       </c>
       <c r="J148" t="n">
-        <v>-59.14</v>
+        <v>-280.9</v>
       </c>
       <c r="K148" t="n">
-        <v>11790.46</v>
+        <v>20170.48</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46175.6875</v>
+        <v>46175.125</v>
       </c>
       <c r="B149" s="1" t="n">
-        <v>46175.70833333334</v>
+        <v>46175.13541666666</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -6522,35 +6522,35 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>4489.918</v>
+        <v>4488.012</v>
       </c>
       <c r="F149" t="n">
-        <v>4488.498</v>
+        <v>4489.012</v>
       </c>
       <c r="G149" t="n">
-        <v>4494.178</v>
+        <v>4486.012</v>
       </c>
       <c r="H149" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="J149" t="n">
-        <v>-28.4</v>
+        <v>200</v>
       </c>
       <c r="K149" t="n">
-        <v>11762.06</v>
+        <v>20370.48</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46175.79166666666</v>
+        <v>46175.38541666666</v>
       </c>
       <c r="B150" s="1" t="n">
-        <v>46175.91666666666</v>
+        <v>46175.40625</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -6559,20 +6559,20 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>BREAKOUT</t>
+          <t>BOUNCE</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>4487.381</v>
+        <v>4526.834</v>
       </c>
       <c r="F150" t="n">
-        <v>4491.498</v>
+        <v>4529.791</v>
       </c>
       <c r="G150" t="n">
-        <v>4475.030000000002</v>
+        <v>4520.919999999999</v>
       </c>
       <c r="H150" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
@@ -6580,141 +6580,141 @@
         </is>
       </c>
       <c r="J150" t="n">
-        <v>-82.34</v>
+        <v>-295.7</v>
       </c>
       <c r="K150" t="n">
-        <v>11679.72</v>
+        <v>20074.78</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46176</v>
+        <v>46175.6875</v>
       </c>
       <c r="B151" s="1" t="n">
-        <v>46176.01041666666</v>
+        <v>46175.70833333334</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>BREAKOUT</t>
+          <t>BOUNCE</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>4475.687</v>
+        <v>4489.918</v>
       </c>
       <c r="F151" t="n">
-        <v>4480.146</v>
+        <v>4488.498</v>
       </c>
       <c r="G151" t="n">
-        <v>4462.31</v>
+        <v>4492.758</v>
       </c>
       <c r="H151" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="J151" t="n">
-        <v>-89.18000000000001</v>
+        <v>284</v>
       </c>
       <c r="K151" t="n">
-        <v>11590.54</v>
+        <v>20358.78</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46176.09375</v>
+        <v>46175.79166666666</v>
       </c>
       <c r="B152" s="1" t="n">
-        <v>46176.10416666666</v>
+        <v>46175.91666666666</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>BOUNCE</t>
+          <t>BREAKOUT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>4478.584</v>
+        <v>4487.381</v>
       </c>
       <c r="F152" t="n">
-        <v>4477.146</v>
+        <v>4491.498</v>
       </c>
       <c r="G152" t="n">
-        <v>4482.898</v>
+        <v>4479.147000000002</v>
       </c>
       <c r="H152" t="n">
-        <v>0.2</v>
+        <v>0.99</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="J152" t="n">
-        <v>86.28</v>
+        <v>-407.58</v>
       </c>
       <c r="K152" t="n">
-        <v>11676.82</v>
+        <v>19951.2</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46176.11458333334</v>
+        <v>46176</v>
       </c>
       <c r="B153" s="1" t="n">
-        <v>46176.125</v>
+        <v>46176.01041666666</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>BOUNCE</t>
+          <t>BREAKOUT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>4482.089</v>
+        <v>4475.687</v>
       </c>
       <c r="F153" t="n">
-        <v>4480.574</v>
+        <v>4480.146</v>
       </c>
       <c r="G153" t="n">
-        <v>4486.634000000001</v>
+        <v>4466.769</v>
       </c>
       <c r="H153" t="n">
-        <v>0.2</v>
+        <v>0.89</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="J153" t="n">
-        <v>90.90000000000001</v>
+        <v>-396.85</v>
       </c>
       <c r="K153" t="n">
-        <v>11767.72</v>
+        <v>19554.35</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46176.28125</v>
+        <v>46176.09375</v>
       </c>
       <c r="B154" s="1" t="n">
-        <v>46176.29166666666</v>
+        <v>46176.10416666666</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -6727,16 +6727,16 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>4462.83</v>
+        <v>4478.584</v>
       </c>
       <c r="F154" t="n">
-        <v>4460.778</v>
+        <v>4477.146</v>
       </c>
       <c r="G154" t="n">
-        <v>4468.985999999999</v>
+        <v>4481.46</v>
       </c>
       <c r="H154" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
@@ -6744,18 +6744,18 @@
         </is>
       </c>
       <c r="J154" t="n">
-        <v>123.12</v>
+        <v>287.6</v>
       </c>
       <c r="K154" t="n">
-        <v>11890.84</v>
+        <v>19841.95</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46176.34375</v>
+        <v>46176.11458333334</v>
       </c>
       <c r="B155" s="1" t="n">
-        <v>46176.35416666666</v>
+        <v>46176.125</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -6768,35 +6768,35 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>4457.252</v>
+        <v>4482.089</v>
       </c>
       <c r="F155" t="n">
-        <v>4454.977</v>
+        <v>4480.574</v>
       </c>
       <c r="G155" t="n">
-        <v>4464.077000000002</v>
+        <v>4485.119000000001</v>
       </c>
       <c r="H155" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="J155" t="n">
-        <v>-45.5</v>
+        <v>303</v>
       </c>
       <c r="K155" t="n">
-        <v>11845.34</v>
+        <v>20144.95</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46176.41666666666</v>
+        <v>46176.28125</v>
       </c>
       <c r="B156" s="1" t="n">
-        <v>46176.42708333334</v>
+        <v>46176.29166666666</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -6809,35 +6809,35 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>4462.809</v>
+        <v>4462.83</v>
       </c>
       <c r="F156" t="n">
         <v>4460.778</v>
       </c>
       <c r="G156" t="n">
-        <v>4468.902</v>
+        <v>4466.933999999999</v>
       </c>
       <c r="H156" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="J156" t="n">
-        <v>-40.62</v>
+        <v>410.4</v>
       </c>
       <c r="K156" t="n">
-        <v>11804.72</v>
+        <v>20555.35</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46176.61458333334</v>
+        <v>46176.34375</v>
       </c>
       <c r="B157" s="1" t="n">
-        <v>46176.625</v>
+        <v>46176.35416666666</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -6850,16 +6850,16 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>4457.258</v>
+        <v>4457.252</v>
       </c>
       <c r="F157" t="n">
         <v>4454.977</v>
       </c>
       <c r="G157" t="n">
-        <v>4464.101</v>
+        <v>4461.802000000001</v>
       </c>
       <c r="H157" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
@@ -6867,18 +6867,18 @@
         </is>
       </c>
       <c r="J157" t="n">
-        <v>-45.62</v>
+        <v>-227.5</v>
       </c>
       <c r="K157" t="n">
-        <v>11759.1</v>
+        <v>20327.85</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46176.92708333334</v>
+        <v>46176.41666666666</v>
       </c>
       <c r="B158" s="1" t="n">
-        <v>46176.9375</v>
+        <v>46176.42708333334</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -6891,39 +6891,39 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>4433.806</v>
+        <v>4462.809</v>
       </c>
       <c r="F158" t="n">
-        <v>4432.129</v>
+        <v>4460.778</v>
       </c>
       <c r="G158" t="n">
-        <v>4438.836999999999</v>
+        <v>4466.871</v>
       </c>
       <c r="H158" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="J158" t="n">
-        <v>100.62</v>
+        <v>-203.1</v>
       </c>
       <c r="K158" t="n">
-        <v>11859.72</v>
+        <v>20124.75</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46177.72916666666</v>
+        <v>46176.61458333334</v>
       </c>
       <c r="B159" s="1" t="n">
-        <v>46177.73958333334</v>
+        <v>46176.625</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -6932,16 +6932,16 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>4476.887</v>
+        <v>4457.258</v>
       </c>
       <c r="F159" t="n">
-        <v>4478.535</v>
+        <v>4454.977</v>
       </c>
       <c r="G159" t="n">
-        <v>4471.942999999999</v>
+        <v>4461.82</v>
       </c>
       <c r="H159" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
@@ -6949,18 +6949,18 @@
         </is>
       </c>
       <c r="J159" t="n">
-        <v>-32.96</v>
+        <v>-228.1</v>
       </c>
       <c r="K159" t="n">
-        <v>11826.76</v>
+        <v>19896.65</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46178.01041666666</v>
+        <v>46176.92708333334</v>
       </c>
       <c r="B160" s="1" t="n">
-        <v>46178.02083333334</v>
+        <v>46176.9375</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -6973,16 +6973,16 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>4457.399</v>
+        <v>4433.806</v>
       </c>
       <c r="F160" t="n">
-        <v>4455.657</v>
+        <v>4432.129</v>
       </c>
       <c r="G160" t="n">
-        <v>4462.625000000001</v>
+        <v>4437.159999999999</v>
       </c>
       <c r="H160" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
@@ -6990,18 +6990,18 @@
         </is>
       </c>
       <c r="J160" t="n">
-        <v>104.52</v>
+        <v>335.4</v>
       </c>
       <c r="K160" t="n">
-        <v>11931.28</v>
+        <v>20232.05</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46178.21875</v>
+        <v>46177.72916666666</v>
       </c>
       <c r="B161" s="1" t="n">
-        <v>46178.22916666666</v>
+        <v>46177.73958333334</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -7014,35 +7014,35 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>4444.726</v>
+        <v>4476.887</v>
       </c>
       <c r="F161" t="n">
-        <v>4446.205</v>
+        <v>4478.535</v>
       </c>
       <c r="G161" t="n">
-        <v>4440.288999999999</v>
+        <v>4473.590999999999</v>
       </c>
       <c r="H161" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="J161" t="n">
-        <v>88.73999999999999</v>
+        <v>-164.8</v>
       </c>
       <c r="K161" t="n">
-        <v>12020.02</v>
+        <v>20067.25</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46178.69791666666</v>
+        <v>46178.01041666666</v>
       </c>
       <c r="B162" s="1" t="n">
-        <v>46178.70833333334</v>
+        <v>46178.02083333334</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -7055,39 +7055,39 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>4344.347</v>
+        <v>4457.399</v>
       </c>
       <c r="F162" t="n">
-        <v>4342.699</v>
+        <v>4455.657</v>
       </c>
       <c r="G162" t="n">
-        <v>4349.291</v>
+        <v>4460.883000000001</v>
       </c>
       <c r="H162" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="J162" t="n">
-        <v>-32.96</v>
+        <v>348.4</v>
       </c>
       <c r="K162" t="n">
-        <v>11987.06</v>
+        <v>20415.65</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46178.80208333334</v>
+        <v>46178.21875</v>
       </c>
       <c r="B163" s="1" t="n">
-        <v>46178.8125</v>
+        <v>46178.22916666666</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -7096,35 +7096,35 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>4323.674</v>
+        <v>4444.726</v>
       </c>
       <c r="F163" t="n">
-        <v>4321.588</v>
+        <v>4446.205</v>
       </c>
       <c r="G163" t="n">
-        <v>4329.932000000001</v>
+        <v>4441.767999999999</v>
       </c>
       <c r="H163" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="J163" t="n">
-        <v>-41.72</v>
+        <v>295.8</v>
       </c>
       <c r="K163" t="n">
-        <v>11945.34</v>
+        <v>20711.45</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46181.28125</v>
+        <v>46178.69791666666</v>
       </c>
       <c r="B164" s="1" t="n">
-        <v>46181.29166666666</v>
+        <v>46178.70833333334</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -7137,68 +7137,150 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>4299.854</v>
+        <v>4344.347</v>
       </c>
       <c r="F164" t="n">
-        <v>4298.402</v>
+        <v>4342.699</v>
       </c>
       <c r="G164" t="n">
-        <v>4304.210000000001</v>
+        <v>4347.643</v>
       </c>
       <c r="H164" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="J164" t="n">
-        <v>87.12</v>
+        <v>-164.8</v>
       </c>
       <c r="K164" t="n">
-        <v>12032.46</v>
+        <v>20546.65</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
+        <v>46178.80208333334</v>
+      </c>
+      <c r="B165" s="1" t="n">
+        <v>46178.8125</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>BOUNCE</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>4323.674</v>
+      </c>
+      <c r="F165" t="n">
+        <v>4321.588</v>
+      </c>
+      <c r="G165" t="n">
+        <v>4327.846</v>
+      </c>
+      <c r="H165" t="n">
+        <v>1</v>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="J165" t="n">
+        <v>-208.6</v>
+      </c>
+      <c r="K165" t="n">
+        <v>20338.05</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="n">
+        <v>46181.28125</v>
+      </c>
+      <c r="B166" s="1" t="n">
+        <v>46181.29166666666</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>BOUNCE</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>4299.854</v>
+      </c>
+      <c r="F166" t="n">
+        <v>4298.402</v>
+      </c>
+      <c r="G166" t="n">
+        <v>4302.758000000001</v>
+      </c>
+      <c r="H166" t="n">
+        <v>1</v>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="J166" t="n">
+        <v>290.4</v>
+      </c>
+      <c r="K166" t="n">
+        <v>20628.45</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="n">
         <v>46181.39583333334</v>
       </c>
-      <c r="B165" s="1" t="n">
+      <c r="B167" s="1" t="n">
         <v>46181.40625</v>
       </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>BOUNCE</t>
-        </is>
-      </c>
-      <c r="E165" t="n">
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>BOUNCE</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
         <v>4293.729</v>
       </c>
-      <c r="F165" t="n">
+      <c r="F167" t="n">
         <v>4291.515</v>
       </c>
-      <c r="G165" t="n">
-        <v>4300.371</v>
-      </c>
-      <c r="H165" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="J165" t="n">
-        <v>132.84</v>
-      </c>
-      <c r="K165" t="n">
-        <v>12165.3</v>
+      <c r="G167" t="n">
+        <v>4298.157</v>
+      </c>
+      <c r="H167" t="n">
+        <v>1</v>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="J167" t="n">
+        <v>442.8</v>
+      </c>
+      <c r="K167" t="n">
+        <v>21071.25</v>
       </c>
     </row>
   </sheetData>
